--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -576,32 +576,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Condo 3 chambres, 1100 pi², 2 balcons – Centre-Sud, près métro Frontenac</t>
+          <t>Grand 4 1/2 avec balcon, wifi et électros neufs inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Centre-Sud</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2553 Avenue Gascon, Montréal, QC H2K 2W5</t>
+          <t>Montréal, QC H1W 3N5</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>quelques min (estimé)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -631,29 +631,29 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-1100pc-3ch-pres-metro-et-plateau/1740479448</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-wifi-electros-inclus/1740319117</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>3 chambres fermées + bureau, 2 balcons, planchers bois franc, grande fenestration, animaux acceptés, dispo 1er août 2026, bail 1 an, secteur vivant à la frontière Plateau/Hochelaga (rue Ontario), aucun stationnement inclus</t>
+          <t>2 chambres fermées + den, grand balcon arrière vue jardin, wifi et électroménagers neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe/climatisation), salle de bain rénovée 2025, non-fumeur, pas d'animaux, dispo 1er août 2026 (possibilité plus tôt), bail 1 an</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6c/6c93d656-ed7d-413a-ac8b-986e4f7f2eda?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/20/2040a77c-67f8-4d3c-8b23-22071ed8ca1b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -673,17 +673,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -698,136 +698,128 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Iberville</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Préfontaine</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -837,32 +829,32 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+          <t>Condo 3 chambres, 1100 pi², 2 balcons – Centre-Sud, près métro Frontenac</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Centre-Sud</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 1M3</t>
+          <t>2553 Avenue Gascon, Montréal, QC H2K 2W5</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -872,7 +864,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -882,7 +874,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -892,29 +884,29 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-1100pc-3ch-pres-metro-et-plateau/1740479448</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+          <t>3 chambres fermées + bureau, 2 balcons, planchers bois franc, grande fenestration, animaux acceptés, dispo 1er août 2026, bail 1 an, secteur vivant à la frontière Plateau/Hochelaga (rue Ontario), aucun stationnement inclus</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6c/6c93d656-ed7d-413a-ac8b-986e4f7f2eda?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -924,32 +916,32 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 Villeray, metro Jarry</t>
+          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R 2E8</t>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -959,17 +951,17 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Iberville</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -979,22 +971,22 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
+          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1011,32 +1003,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1046,42 +1038,42 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1098,32 +1090,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1133,17 +1125,17 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1153,22 +1145,22 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1185,27 +1177,27 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>Grand 6 1/2 Villeray, metro Jarry</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>Montréal, QC H2R 2E8</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1220,7 +1212,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1230,7 +1222,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1240,22 +1232,22 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
         </is>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1264,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 1000 pi², balcon – Rosemont/Beaubien</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Rue de Normanville, Montréal, QC H2S 2B5</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1307,27 +1299,27 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/Beaubien</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appart-5-1-2-a-louer-3-bed-apartment-for-rent-la-petite-patrie/1740477077</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1337,10 +1329,14 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>1 mois gratuit 1ère année (régulier 2160$), animaux non acceptés, près du parc Père-Marquette, libre 12 juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr"/>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1355,22 +1351,22 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1385,22 +1381,22 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -1410,7 +1406,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1420,12 +1416,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1442,32 +1438,32 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1477,27 +1473,27 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -1507,10 +1503,14 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr"/>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1525,27 +1525,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>5 1/2, 1000 pi², balcon – Rosemont/Beaubien</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>Rue de Normanville, Montréal, QC H2S 2B5</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Rosemont/Beaubien</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appart-5-1-2-a-louer-3-bed-apartment-for-rent-la-petite-patrie/1740477077</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -1590,14 +1590,10 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>1 mois gratuit 1ère année (régulier 2160$), animaux non acceptés, près du parc Père-Marquette, libre 12 juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1612,27 +1608,27 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1642,22 +1638,22 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1677,12 +1673,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1695,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1709,32 +1705,32 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1744,17 +1740,17 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1764,14 +1760,10 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1786,27 +1778,27 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1821,7 +1813,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1831,7 +1823,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1841,7 +1833,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1851,19 +1843,19 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1873,7 +1865,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1883,22 +1875,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1908,7 +1900,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1918,7 +1910,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1928,22 +1920,22 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1960,77 +1952,77 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -2047,22 +2039,22 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2072,7 +2064,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2082,7 +2074,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -2092,7 +2084,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -2102,29 +2094,29 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2134,27 +2126,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2169,27 +2161,27 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2199,12 +2191,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2221,32 +2213,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -2256,27 +2248,27 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2286,12 +2278,12 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2308,32 +2300,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2343,17 +2335,17 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2363,7 +2355,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2373,12 +2365,12 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2395,27 +2387,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2430,27 +2422,27 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2460,19 +2452,19 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2482,22 +2474,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2507,7 +2499,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2517,7 +2509,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2527,32 +2519,32 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2561,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2579,32 +2571,32 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2614,7 +2606,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2624,22 +2616,22 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2656,27 +2648,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2686,22 +2678,22 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>n/d (grande cour arrière privée)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2711,29 +2703,29 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2743,27 +2735,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2773,22 +2765,22 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2798,7 +2790,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2808,12 +2800,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2830,62 +2822,62 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ meublé et entièrement rénové</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2895,10 +2887,14 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="inlineStr"/>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2913,62 +2909,62 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d (grande cour arrière privée)</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
@@ -2978,10 +2974,14 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr"/>
+          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3026,22 +3026,22 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -3051,22 +3051,22 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>Grand 5½ meublé et entièrement rénové</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -3093,37 +3093,37 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -3133,29 +3133,25 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3170,27 +3166,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3200,54 +3196,50 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
-        </is>
-      </c>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3257,7 +3249,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -3267,67 +3259,67 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>oui (patio arrière)</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3344,42 +3336,42 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -3389,32 +3381,32 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3431,52 +3423,52 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal</t>
-        </is>
-      </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3486,114 +3478,375 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>62 rue Rachel Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>4275 Rue de Bordeaux, Montréal</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N39" s="7" t="inlineStr">
         <is>
           <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P36" s="6" t="inlineStr">
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q36"/>
+  <autoFilter ref="A1:Q39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -3630,6 +3883,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -36,7 +36,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -46,11 +46,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,19 +61,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -566,42 +552,42 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>NOUVEAU</t>
+          <t>vu</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Grand 4 1/2 avec balcon, wifi et électros neufs inclus – Hochelaga</t>
+          <t>Condo 3 chambres, 1100 pi², 2 balcons – Centre-Sud, près métro Frontenac</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Centre-Sud</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3N5</t>
+          <t>2553 Avenue Gascon, Montréal, QC H2K 2W5</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -611,7 +597,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -621,7 +607,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>quelques min (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -631,64 +617,64 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-wifi-electros-inclus/1740319117</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-1100pc-3ch-pres-metro-et-plateau/1740479448</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2 chambres fermées + den, grand balcon arrière vue jardin, wifi et électroménagers neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe/climatisation), salle de bain rénovée 2025, non-fumeur, pas d'animaux, dispo 1er août 2026 (possibilité plus tôt), bail 1 an</t>
+          <t>3 chambres fermées + bureau, 2 balcons, planchers bois franc, grande fenestration, animaux acceptés, dispo 1er août 2026, bail 1 an, secteur vivant à la frontière Plateau/Hochelaga (rue Ontario), aucun stationnement inclus</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/20/2040a77c-67f8-4d3c-8b23-22071ed8ca1b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6c/6c93d656-ed7d-413a-ac8b-986e4f7f2eda?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NOUVEAU</t>
+          <t>vu</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -698,12 +684,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -713,3133 +699,3133 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NOUVEAU</t>
+          <t>vu</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Préfontaine</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Condo 3 chambres, 1100 pi², 2 balcons – Centre-Sud, près métro Frontenac</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Centre-Sud</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2553 Avenue Gascon, Montréal, QC H2K 2W5</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Grand 6 1/2 Villeray, metro Jarry</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Montréal, QC H2R 2E8</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Frontenac</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-1100pc-3ch-pres-metro-et-plateau/1740479448</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>3 chambres fermées + bureau, 2 balcons, planchers bois franc, grande fenestration, animaux acceptés, dispo 1er août 2026, bail 1 an, secteur vivant à la frontière Plateau/Hochelaga (rue Ontario), aucun stationnement inclus</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6c/6c93d656-ed7d-413a-ac8b-986e4f7f2eda?rule=kijijica-960-jpg</t>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Grand 4 1/2 avec balcon, wifi et électros neufs inclus – Hochelaga</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Montréal, QC H1W 3N5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>900</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Iberville</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Joliette ou Pie-IX</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>quelques min (estimé)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-wifi-electros-inclus/1740319117</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2 chambres fermées + den, grand balcon arrière vue jardin, wifi et électroménagers neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe/climatisation), salle de bain rénovée 2025, non-fumeur, pas d'animaux, dispo 1er août 2026 (possibilité plus tôt), bail 1 an</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/20/2040a77c-67f8-4d3c-8b23-22071ed8ca1b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3439 Rue William-Tremblay, Montréal</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H1W 1M3</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Préfontaine</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Grand 6 1/2 Villeray, metro Jarry</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H2R 2E8</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Joliette/Pie-IX</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Joliette/Pie-IX</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>n/d (bus ~20 min)</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2, 1000 pi², balcon – Rosemont/Beaubien</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Rue de Normanville, Montréal, QC H2S 2B5</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Laurier</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont/Beaubien</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>n/d (bus ~20 min)</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appart-5-1-2-a-louer-3-bed-apartment-for-rent-la-petite-patrie/1740477077</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>1 mois gratuit 1ère année (régulier 2160$), animaux non acceptés, près du parc Père-Marquette, libre 12 juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2, 1000 pi², balcon – Rosemont/Beaubien</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Rue de Normanville, Montréal, QC H2S 2B5</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Montréal, QC H1W 3A8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont/Beaubien</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appart-5-1-2-a-louer-3-bed-apartment-for-rent-la-petite-patrie/1740477077</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>1 mois gratuit 1ère année (régulier 2160$), animaux non acceptés, près du parc Père-Marquette, libre 12 juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H1W 3A8</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3602 rue de Rouen, Montréal</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Joliette</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>3602 rue de Rouen, Montréal</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2150</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>secteur métro Beaubien, H2S 2J5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>LogisQuébec</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>rue Marie-Anne, H2H 1M9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Pie-IX</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Pie-IX</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Iberville</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5 (estimé)</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2195</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>974</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>946</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Beaubien</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>8 (estimé)</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Beaubien</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>D'Iberville</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>bleue</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>DuProprio</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P23" s="6" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2195</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Préfontaine</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
         <is>
           <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
-      <c r="Q24" s="5" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2195</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Préfontaine</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Villeray</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2305</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Jarry</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
-      <c r="Q26" s="5" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2150</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Joliette</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>10 (estimé)</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>900</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Pie-IX</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>10 (estimé)</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P28" s="6" t="inlineStr">
+      <c r="P28" s="3" t="inlineStr">
         <is>
           <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
-      <c r="Q28" s="5" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1950</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>950</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>n/d (grande cour arrière privée)</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Joliette</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>9 (estimé)</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr">
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Laurier</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
+      <c r="P30" s="3" t="inlineStr">
         <is>
           <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
-      <c r="Q30" s="5" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Grand 5½ meublé et entièrement rénové</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Villeray</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>2265</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Saint-Michel</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>bleue</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>LogisQuébec</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Villeray</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>2300</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Jarry</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>LogisQuébec</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P32" s="6" t="inlineStr">
+      <c r="P32" s="3" t="inlineStr">
         <is>
           <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
         </is>
       </c>
-      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>5 1/2 rénové, stationnement, patio – Plateau</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>oui (patio arrière)</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P33" s="6" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Villeray</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Montréal, QC H2R</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Jarry</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P34" s="6" t="inlineStr">
+      <c r="P34" s="3" t="inlineStr">
         <is>
           <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>995</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>DuProprio</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P35" s="6" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2150</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>12 (estimé)</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>DuProprio</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P36" s="6" t="inlineStr">
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2195</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>8 (estimé)</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>DuProprio</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P37" s="6" t="inlineStr">
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Mont-Royal</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>10 (estimé)</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>DuProprio</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P38" s="6" t="inlineStr">
+      <c r="P38" s="3" t="inlineStr">
         <is>
           <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
-      <c r="Q38" s="5" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P39" s="6" t="inlineStr">
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1001,7 +1001,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Condo 3 chambres, 1100 pi², 2 balcons – Centre-Sud, près métro Frontenac</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Centre-Sud</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2553 Avenue Gascon, Montréal, QC H2K 2W5</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-1100pc-3ch-pres-metro-et-plateau/1740479448</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées + bureau, 2 balcons, planchers bois franc, grande fenestration, animaux acceptés, dispo 1er août 2026, bail 1 an, secteur vivant à la frontière Plateau/Hochelaga (rue Ontario), aucun stationnement inclus</t>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/6c/6c93d656-ed7d-413a-ac8b-986e4f7f2eda?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1098,32 +1098,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1185,32 +1185,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+          <t>Grand 6 1/2 Villeray, metro Jarry</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 1M3</t>
+          <t>Montréal, QC H2R 2E8</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -1250,19 +1250,19 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
         </is>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 Villeray, metro Jarry</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R 2E8</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1307,44 +1307,40 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1359,27 +1355,27 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 1/2 avec balcon, wifi et électros neufs inclus – Hochelaga</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3N5</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1394,7 +1390,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1404,17 +1400,17 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>quelques min (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-wifi-electros-inclus/1740319117</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1424,19 +1420,15 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + den, grand balcon arrière vue jardin, wifi et électroménagers neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe/climatisation), salle de bain rénovée 2025, non-fumeur, pas d'animaux, dispo 1er août 2026 (possibilité plus tôt), bail 1 an</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/20/2040a77c-67f8-4d3c-8b23-22071ed8ca1b?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1446,27 +1438,27 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1481,7 +1473,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1491,17 +1483,17 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -1511,15 +1503,19 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr"/>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1529,32 +1525,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1564,27 +1560,27 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -1594,10 +1590,14 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr"/>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1612,32 +1612,32 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1699,22 +1699,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1786,32 +1786,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1851,14 +1851,10 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1873,27 +1869,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 1000 pi², balcon – Rosemont/Beaubien</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Rue de Normanville, Montréal, QC H2S 2B5</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1908,7 +1904,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/Beaubien</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1918,7 +1914,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1928,7 +1924,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appart-5-1-2-a-louer-3-bed-apartment-for-rent-la-petite-patrie/1740477077</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -1938,10 +1934,14 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>1 mois gratuit 1ère année (régulier 2160$), animaux non acceptés, près du parc Père-Marquette, libre 12 juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr"/>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1986,22 +1986,22 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2053,32 +2053,32 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2108,10 +2108,14 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr"/>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2126,27 +2130,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2161,7 +2165,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -2171,7 +2175,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2181,7 +2185,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2191,19 +2195,19 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2213,32 +2217,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -2248,17 +2252,17 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Iberville</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -2268,29 +2272,29 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2300,77 +2304,77 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2387,32 +2391,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2422,7 +2426,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2432,39 +2436,39 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2474,27 +2478,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2509,17 +2513,17 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Iberville</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2529,7 +2533,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2539,19 +2543,19 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2561,27 +2565,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2596,27 +2600,27 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2626,12 +2630,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
@@ -2648,32 +2652,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2683,27 +2687,27 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2713,12 +2717,12 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -2735,32 +2739,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2770,17 +2774,17 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2790,7 +2794,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2800,12 +2804,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2822,27 +2826,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2857,27 +2861,27 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2887,19 +2891,19 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2909,22 +2913,22 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2934,7 +2938,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2944,7 +2948,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2954,32 +2958,32 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3006,32 +3010,32 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -3041,7 +3045,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -3051,22 +3055,22 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3083,27 +3087,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -3113,22 +3117,22 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d (grande cour arrière privée)</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -3138,29 +3142,29 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3170,27 +3174,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3200,22 +3204,22 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
@@ -3225,7 +3229,7 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3235,12 +3239,12 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3257,62 +3261,62 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>Grand 5½ meublé et entièrement rénové</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3322,14 +3326,10 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3344,62 +3344,62 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>n/d (grande cour arrière privée)</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>9 (estimé)</t>
-        </is>
-      </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3409,14 +3409,10 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
-        </is>
-      </c>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3431,7 +3427,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3441,12 +3437,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3461,22 +3457,22 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui (patio arrière)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3486,22 +3482,22 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3514,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ meublé et entièrement rénové</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3528,37 +3524,37 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -3568,25 +3564,29 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
-        </is>
-      </c>
-      <c r="Q36" s="5" t="inlineStr"/>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3601,80 +3601,84 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="inlineStr"/>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3684,7 +3688,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3694,67 +3698,67 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
@@ -3771,42 +3775,42 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -3816,32 +3820,32 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
@@ -3858,27 +3862,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -3893,17 +3897,17 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
@@ -3913,29 +3917,29 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3945,22 +3949,22 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3980,308 +3984,47 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>62 rue Rachel Est, Montréal</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2195</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N42" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
-        </is>
-      </c>
-      <c r="Q42" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
-        </is>
-      </c>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>1889 Rue des Carrières, Montréal</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N44" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q44"/>
+  <autoFilter ref="A1:Q41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -4323,9 +4066,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -576,54 +576,54 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Crémazie</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
@@ -631,7 +631,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
         </is>
       </c>
     </row>
@@ -663,32 +663,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -750,52 +750,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -847,154 +847,154 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Jarry ou Crémazie</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Laurier</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1307,27 +1307,27 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1337,15 +1337,19 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr"/>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1355,42 +1359,42 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1400,17 +1404,17 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1420,15 +1424,19 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr"/>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1438,27 +1446,27 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1473,7 +1481,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1483,17 +1491,17 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -1503,19 +1511,15 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1525,32 +1529,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1560,27 +1564,27 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -1590,14 +1594,10 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1612,32 +1612,32 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
@@ -1699,22 +1699,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1786,32 +1786,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1851,10 +1851,14 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr"/>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1869,27 +1873,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1899,22 +1903,22 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1924,7 +1928,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -1934,12 +1938,12 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1956,32 +1960,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1991,27 +1995,27 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2021,14 +2025,10 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2043,27 +2043,27 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2073,32 +2073,32 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2195,19 +2195,19 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2217,84 +2217,84 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Iberville</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2314,22 +2314,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2359,29 +2359,29 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2391,27 +2391,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2478,27 +2478,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Iberville</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2543,19 +2543,19 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2565,27 +2565,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2600,27 +2600,27 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2652,32 +2652,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2687,27 +2687,27 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2739,32 +2739,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2774,17 +2774,17 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2826,27 +2826,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2861,27 +2861,27 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2891,19 +2891,19 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2913,22 +2913,22 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2958,32 +2958,32 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3010,32 +3010,32 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -3055,22 +3055,22 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3087,27 +3087,27 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>n/d (grande cour arrière privée)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -3142,29 +3142,29 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3239,19 +3239,19 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3261,22 +3261,22 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ meublé et entièrement rénové</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3296,27 +3296,27 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3326,10 +3326,14 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="inlineStr"/>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3344,62 +3348,62 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3409,10 +3413,14 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q34" s="5" t="inlineStr"/>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3427,27 +3435,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -3457,22 +3465,22 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>n/d (grande cour arrière privée)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3482,22 +3490,22 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3514,27 +3522,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -3544,12 +3552,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -3559,7 +3567,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
@@ -3569,22 +3577,22 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3601,27 +3609,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>Grand 5½ meublé et entièrement rénové</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -3631,54 +3639,50 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Saint-Michel</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3688,22 +3692,22 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -3718,12 +3722,12 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -3733,34 +3737,30 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
-        </is>
-      </c>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3785,67 +3785,67 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>oui (patio arrière)</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3862,42 +3862,42 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3907,32 +3907,32 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3949,82 +3949,430 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>5472 1ere Avenue, Montréal</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>62 rue Rachel Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>4275 Rue de Bordeaux, Montréal</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
           <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P41" s="6" t="inlineStr">
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q41"/>
+  <autoFilter ref="A1:Q45"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -4066,6 +4414,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -576,32 +576,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -611,42 +611,42 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Crémazie</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
         </is>
       </c>
     </row>
@@ -663,32 +663,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Crémazie</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -718,22 +718,22 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
         </is>
       </c>
     </row>
@@ -750,27 +750,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -837,852 +837,860 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5048 rue Rivard (H2J 2M9)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Fabre</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Villeray</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Jean-Talon</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>orange/bleue</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Rue Sewell (H2W 1V9)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Ville-Marie (Centre-Sud)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Papineau</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1478 rue Dézéry</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Préfontaine</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Beaubien</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3855 rue St-André (H2L 3V9)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H1W 1M3</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Grand 6 1/2 Villeray, metro Jarry</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H2R 2E8</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Pie-IX</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>LogisQuébec</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Préfontaine</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>LogisQuébec</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Joliette/Pie-IX</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
@@ -1699,22 +1707,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1734,17 +1742,17 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1754,22 +1762,22 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1786,32 +1794,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1821,17 +1829,17 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1841,29 +1849,29 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1873,27 +1881,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1903,22 +1911,22 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1928,22 +1936,22 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1960,32 +1968,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>Grand 6 1/2 Villeray, metro Jarry</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>Montréal, QC H2R 2E8</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1995,40 +2003,44 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr"/>
+          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2043,27 +2055,27 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -2078,17 +2090,17 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -2098,7 +2110,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2108,12 +2120,12 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2130,27 +2142,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2165,7 +2177,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -2175,7 +2187,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2185,7 +2197,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2195,12 +2207,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2229,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2227,32 +2239,32 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -2262,17 +2274,17 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2282,19 +2294,19 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2304,27 +2316,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2334,17 +2346,17 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -2359,7 +2371,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2369,19 +2381,19 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2391,27 +2403,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2426,49 +2438,45 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Crémazie</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2478,27 +2486,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2513,49 +2521,45 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Iberville</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2565,52 +2569,52 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2620,22 +2624,22 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2652,27 +2656,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2687,44 +2691,40 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2749,22 +2749,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2794,29 +2794,29 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2826,32 +2826,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2861,42 +2861,42 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2913,27 +2913,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2948,42 +2948,42 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3010,17 +3010,17 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -3045,32 +3045,32 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -3087,32 +3087,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -3142,29 +3142,29 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,27 +3174,27 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
@@ -3229,29 +3229,29 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3261,27 +3261,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -3316,29 +3316,29 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3348,22 +3348,22 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Iberville</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3403,22 +3403,22 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3435,27 +3435,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -3465,54 +3465,54 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>n/d (grande cour arrière privée)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
@@ -3577,22 +3577,22 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3609,22 +3609,22 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ meublé et entièrement rénové</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3644,40 +3644,44 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="inlineStr"/>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3692,22 +3696,22 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -3727,45 +3731,49 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q38" s="5" t="inlineStr"/>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3775,27 +3783,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -3805,47 +3813,47 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3870,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3872,17 +3880,17 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -3892,7 +3900,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -3907,7 +3915,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
@@ -3917,29 +3925,29 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3949,32 +3957,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3984,49 +3992,49 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4036,77 +4044,77 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4123,77 +4131,77 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>n/d (grande cour arrière privée)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4218,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4220,159 +4228,934 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>oui (petit balcon cuisine)</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5½ meublé et entièrement rénové</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2265</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Saint-Michel</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>5½ 2e étage Jarry Est rénové</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>582 rue Jarry Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>oui (patio arrière)</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Montréal, QC H2R</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>5472 1ere Avenue, Montréal</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+        </is>
+      </c>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>4275 Rue de Bordeaux, Montréal</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+        </is>
+      </c>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>62 rue Rachel Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+        </is>
+      </c>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="N54" s="7" t="inlineStr">
         <is>
           <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P45" s="6" t="inlineStr">
+      <c r="P54" s="6" t="inlineStr">
         <is>
           <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
-      <c r="Q45" s="5" t="inlineStr">
+      <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q45"/>
+  <autoFilter ref="A1:Q54"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -4418,6 +5201,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -576,22 +576,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
+          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -611,42 +611,42 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -663,32 +663,32 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -698,42 +698,42 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Crémazie</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -750,27 +750,27 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
+          <t>n/d (Montréal, QC H2R)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -780,22 +780,22 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -805,22 +805,22 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -837,27 +837,27 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -882,32 +882,32 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -924,773 +924,773 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Rue Beaubien (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
           <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Crémazie</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Montréal, QC H1W 1M3</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Joliette ou Pie-IX</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Laurier</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Fabre</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Jean-Talon</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>orange/bleue</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Rue Sewell (H2W 1V9)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Ville-Marie (Centre-Sud)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Papineau</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1478 rue Dézéry</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Préfontaine</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 1M3</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1839,32 +1839,32 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1936,29 +1936,29 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1968,32 +1968,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 Villeray, metro Jarry</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R 2E8</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2003,49 +2003,45 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740222569</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er août 2026 (ou 1er juillet), 2 balcons (avant + grand arrière), 3 chambres fermées, électros non inclus mais négociable, pas d'animaux, non-fumeur, chauffage/électricité aux frais du locataire</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/41/41b6a01a-67b3-4d74-8966-ac23a1a991aa?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2055,32 +2051,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2090,27 +2086,27 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2120,14 +2116,10 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2142,27 +2134,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2172,22 +2164,22 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2197,7 +2189,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2207,12 +2199,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2221,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2239,12 +2231,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2264,7 +2256,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -2274,17 +2266,17 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2294,19 +2286,15 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2316,27 +2304,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2346,22 +2334,22 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2371,7 +2359,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2381,19 +2369,19 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2403,7 +2391,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2413,12 +2401,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2428,7 +2416,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2438,27 +2426,27 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2468,15 +2456,19 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr"/>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2486,7 +2478,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2496,12 +2488,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2511,7 +2503,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2521,27 +2513,27 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2551,10 +2543,14 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="inlineStr"/>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2569,7 +2565,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2579,17 +2575,17 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2599,12 +2595,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2614,17 +2610,17 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2634,12 +2630,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -2656,32 +2652,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2691,27 +2687,27 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2721,15 +2717,19 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="inlineStr"/>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2739,27 +2739,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2774,42 +2774,42 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
         </is>
       </c>
     </row>
@@ -2826,32 +2826,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2871,39 +2871,39 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2913,27 +2913,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2943,47 +2943,47 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
         </is>
       </c>
     </row>
@@ -3000,77 +3000,77 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3087,22 +3087,22 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -3132,39 +3132,39 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Iberville</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3261,27 +3261,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -3296,27 +3296,27 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
@@ -3348,27 +3348,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Iberville</t>
+          <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
+          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3435,32 +3435,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -3470,27 +3470,27 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -3500,19 +3500,19 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3522,17 +3522,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -3587,19 +3587,19 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3644,27 +3644,27 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
@@ -3696,32 +3696,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3731,12 +3731,12 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -3793,74 +3793,74 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Jarry ou Crémazie</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3870,27 +3870,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>Rue Sewell (H2W 1V9)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3920,27 +3920,27 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
         </is>
       </c>
     </row>
@@ -4131,27 +4131,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec garage, grande cour – Hochelaga (Place Valois)</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N6, angle Bourbonnière/Ontario)</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4161,22 +4161,22 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>n/d (grande cour arrière privée)</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-avec-garage-a-louer-dans-hochelaga-mainsonneuve/1739944242</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Chauffage et climatisation centrale inclus, chats seulement (pas de chiens), 2 places de stationnement + 1 garage, libre 1er août 2026, près Place Valois</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/3e/3efd086c-a651-43a1-8291-a49f0c1d38d5?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4218,27 +4218,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -4248,22 +4248,22 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
@@ -4283,19 +4283,19 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4305,22 +4305,22 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4330,37 +4330,37 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -4370,19 +4370,15 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4392,22 +4388,22 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Grand 5½ meublé et entièrement rénové</t>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>13e Avenue, Montréal (près métro Saint-Michel)</t>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4422,17 +4418,17 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Saint-Michel</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -4442,30 +4438,34 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353226</t>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres, meublé, laveuse-sécheuse, comptoirs quartz, balcon + terrasse, métro Saint-Michel à 394 m, cession de bail jusqu'au 30 juin 2027, pas d'animaux, limite est de Villeray</t>
-        </is>
-      </c>
-      <c r="Q46" s="5" t="inlineStr"/>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4475,22 +4475,22 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>1478 rue Dézéry</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4500,55 +4500,59 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="inlineStr"/>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4558,27 +4562,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -4588,32 +4592,32 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -4623,12 +4627,12 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
         </is>
       </c>
     </row>
@@ -4645,27 +4649,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4675,47 +4679,47 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui (patio arrière)</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
-        </is>
-      </c>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4732,62 +4736,62 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -4797,12 +4801,12 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4819,52 +4823,52 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal</t>
-        </is>
-      </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
@@ -4874,29 +4878,29 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4906,7 +4910,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -4916,12 +4920,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>3855 rue St-André (H2L 3V9)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -4931,7 +4935,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -4941,7 +4945,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -4951,17 +4955,17 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
@@ -4971,12 +4975,12 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4997,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -5003,12 +5007,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5028,7 +5032,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -5038,7 +5042,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
@@ -5048,7 +5052,7 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -5058,104 +5062,278 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+        </is>
+      </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>62 rue Rachel Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+        </is>
+      </c>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr">
+      <c r="N56" s="7" t="inlineStr">
         <is>
           <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P54" s="6" t="inlineStr">
+      <c r="P56" s="6" t="inlineStr">
         <is>
           <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
-      <c r="Q54" s="5" t="inlineStr">
+      <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q54"/>
+  <autoFilter ref="A1:Q56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -5210,6 +5388,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q56"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -576,32 +576,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
+          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>4224 Rue de Bellechasse, Montréal</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -611,27 +611,27 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Fabre (à vérifier)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -641,19 +641,19 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
+          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -663,27 +663,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
+          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
+          <t>3528 Avenue Coloniale, Montréal</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -718,29 +718,29 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
+          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -750,84 +750,84 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
+          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R)</t>
+          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Papineau ou Beaudry</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
+          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -837,22 +837,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
+          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
+          <t>6904 Rue Hutchison, Montréal</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Parc ou Acadie</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -902,19 +902,19 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
+          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -924,947 +924,947 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Rue Beaubien (Montréal, QC)</t>
+          <t>5342 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6 (estimé)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3514 Avenue De Lorimier, Montréal</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Mont-Royal (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6904, 23e Avenue, Montréal</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>oui (terrasse sur le toit)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Beaubien ou Rosemont (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Ville-Marie (Centre-Sud)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2121 Avenue Papineau, app. 106, Montréal</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Papineau</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11 (estimé)</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6525 Rue Fabre, app. 2, Montréal</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Beaubien (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6391 Avenue Henri-Julien, Montréal</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Talon (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Pie-IX (mentionné dans le titre)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>verte</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Crémazie</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H1W 1M3</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Location 4 et demi Plateau, pet friendly</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>5 1/2 Rosemont avec cour privée</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Joliette ou Pie-IX</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Laurier</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>n/d (bus ~20 min)</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Joliette/Pie-IX</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
         </is>
       </c>
     </row>
@@ -1881,27 +1881,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1926,39 +1926,39 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1968,32 +1968,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2003,45 +2003,49 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Crémazie</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr"/>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2051,32 +2055,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2086,12 +2090,12 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -2101,25 +2105,29 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr"/>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2134,7 +2142,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2144,27 +2152,27 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -2179,7 +2187,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2189,29 +2197,29 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2221,32 +2229,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -2256,45 +2264,49 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr"/>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2304,32 +2316,32 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2339,7 +2351,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -2349,7 +2361,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2359,7 +2371,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2369,12 +2381,12 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2391,32 +2403,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2426,17 +2438,17 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -2446,7 +2458,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2456,19 +2468,19 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2478,32 +2490,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2513,7 +2525,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2523,7 +2535,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2533,7 +2545,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2543,12 +2555,12 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -2565,27 +2577,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2595,32 +2607,32 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2630,12 +2642,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2652,27 +2664,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2687,7 +2699,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2697,7 +2709,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2707,7 +2719,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2717,19 +2729,19 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2739,7 +2751,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2749,22 +2761,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2774,7 +2786,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2784,32 +2796,32 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
@@ -2826,84 +2838,84 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2913,47 +2925,47 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2963,34 +2975,30 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -3000,27 +3008,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -3035,44 +3043,40 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3087,52 +3091,52 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -3142,29 +3146,29 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,22 +3178,22 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 (2 chambres), 900 pi², balcon, tout inclus – Rosemont (rue Dandurand)</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3209,44 +3213,40 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Iberville</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-a-louer-2-chambres-rosemont-petite-patrie-tout-inclus/1739170766</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Construit 2012, tout inclus (chauffage, hydro, eau, wifi, climatisation), semi-meublé (électros + meubles salon/cuisine, matelas non inclus), animaux limités, dispo 1er juillet 2026, à 5-10 min à pied des commerces/restos de la rue Masson</t>
-        </is>
-      </c>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bacee7d5-1abf-4a36-80b6-12877aa40971?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3296,49 +3296,49 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N33" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
-        </is>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3403,22 +3403,22 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3435,27 +3435,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -3470,42 +3470,42 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -3567,39 +3567,39 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Crémazie</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -3654,39 +3654,39 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3696,32 +3696,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3731,27 +3731,27 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
         </is>
       </c>
     </row>
@@ -3783,32 +3783,32 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3838,22 +3838,22 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
@@ -3870,32 +3870,32 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Rue Sewell (H2W 1V9)</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3925,29 +3925,29 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3957,27 +3957,27 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4044,27 +4044,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
@@ -4099,22 +4099,22 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4131,27 +4131,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4161,47 +4161,47 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
@@ -4218,27 +4218,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -4253,17 +4253,17 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Mont-Royal ou Laurier</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4273,22 +4273,22 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4305,22 +4305,22 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4340,45 +4340,49 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr"/>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4388,22 +4392,22 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4418,12 +4422,12 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -4433,32 +4437,32 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4475,84 +4479,84 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>1478 rue Dézéry</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4562,27 +4566,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -4592,12 +4596,12 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -4607,39 +4611,39 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4649,27 +4653,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4679,54 +4683,54 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -4746,74 +4750,74 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -4823,32 +4827,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>Rue Sewell (H2W 1V9)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -4858,42 +4862,42 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4914,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -4920,22 +4924,22 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -4945,7 +4949,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -4955,32 +4959,32 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4997,32 +5001,32 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -5032,12 +5036,12 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -5047,34 +5051,34 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -5084,7 +5088,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -5094,74 +5098,74 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>oui (petit balcon cuisine)</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>12 (estimé)</t>
-        </is>
-      </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5171,22 +5175,22 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5196,52 +5200,52 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5258,82 +5262,1296 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
+          <t>5½ 2e étage Jarry Est rénové</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>582 rue Jarry Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>LogisQuébec</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H2R)</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
+        </is>
+      </c>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Ville-Marie (Centre-Sud)</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Papineau</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>1478 rue Dézéry</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Préfontaine</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>oui (patio arrière)</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Montréal, QC H2R</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>5472 1ere Avenue, Montréal</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+        </is>
+      </c>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>3855 rue St-André (H2L 3V9)</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>4275 Rue de Bordeaux, Montréal</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+        </is>
+      </c>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>12 (estimé)</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+        </is>
+      </c>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>62 rue Rachel Est, Montréal</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+        </is>
+      </c>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Rue Beaubien (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
           <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>2375</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>Centris</t>
         </is>
       </c>
-      <c r="N56" s="7" t="inlineStr">
+      <c r="N70" s="7" t="inlineStr">
         <is>
           <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O70" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P56" s="6" t="inlineStr">
+      <c r="P70" s="6" t="inlineStr">
         <is>
           <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
-      <c r="Q56" s="5" t="inlineStr">
+      <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q56"/>
+  <autoFilter ref="A1:Q70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -5390,6 +6608,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -576,27 +576,27 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
+          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>4224 Rue de Bellechasse, Montréal</t>
+          <t>Villeray (adresse exacte n/d), Montréal</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Fabre (à vérifier)</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -621,32 +621,32 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
+          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -663,27 +663,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
+          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>3528 Avenue Coloniale, Montréal</t>
+          <t>8360 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -708,32 +708,32 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>2 (estimé)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
+          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
+          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud/Village)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
+          <t>7186 Rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -785,27 +785,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Papineau ou Beaudry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
+          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
         </is>
       </c>
     </row>
@@ -837,1041 +837,1041 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
+          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6904 Rue Hutchison, Montréal</t>
+          <t>7639 Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Talon ou Jarry (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5 (estimé)</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Crémazie</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Montréal, QC H1W 1M3</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Parc ou Acadie</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>4224 Rue de Bellechasse, Montréal</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Fabre (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Hochelaga-Maisonneuve</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Joliette ou Pie-IX</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5342 Rue Saint-Denis, Montréal</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Laurier</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6 (estimé)</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3514 Avenue De Lorimier, Montréal</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Mont-Royal (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12 (estimé)</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6904, 23e Avenue, Montréal</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>oui (terrasse sur le toit)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Beaubien ou Rosemont (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Ville-Marie (Centre-Sud)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2121 Avenue Papineau, app. 106, Montréal</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Papineau</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>11 (estimé)</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6525 Rue Fabre, app. 2, Montréal</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Beaubien (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2292</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6391 Avenue Henri-Julien, Montréal</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Jean-Talon (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>orange/bleue</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Pie-IX (mentionné dans le titre)</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Location 4 et demi Plateau, pet friendly</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Le Plateau-Mont-Royal</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2150</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>NOUVEAU</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>5 1/2 Rosemont avec cour privée</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>n/d (bus ~20 min)</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1891,22 +1891,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1931,27 +1931,27 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
@@ -1968,52 +1968,52 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Crémazie</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2023,29 +2023,29 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2055,32 +2055,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -2105,34 +2105,30 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2142,32 +2138,32 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 1M3</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2177,7 +2173,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -2187,39 +2183,35 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2229,27 +2221,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2259,22 +2251,22 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -2284,29 +2276,29 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2316,27 +2308,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2351,27 +2343,27 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2381,19 +2373,15 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2403,32 +2391,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2438,17 +2426,17 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -2458,7 +2446,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2468,12 +2456,12 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2490,32 +2478,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2525,7 +2513,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2535,7 +2523,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2545,7 +2533,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2555,12 +2543,12 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2577,27 +2565,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2612,12 +2600,12 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2632,7 +2620,7 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2642,12 +2630,12 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2664,27 +2652,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2694,32 +2682,32 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2729,12 +2717,12 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -2751,32 +2739,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2786,27 +2774,27 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2816,19 +2804,19 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2838,84 +2826,84 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>3528 Avenue Coloniale, Montréal</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2925,32 +2913,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2960,7 +2948,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Papineau ou Beaudry</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2970,35 +2958,39 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr"/>
+          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -3008,32 +3000,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3043,7 +3035,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -3053,35 +3045,39 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="inlineStr"/>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3091,84 +3087,84 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3178,75 +3174,79 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q32" s="5" t="inlineStr"/>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -3316,29 +3316,29 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3348,22 +3348,22 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3403,22 +3403,22 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3435,32 +3435,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -3470,42 +3470,42 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
@@ -3577,22 +3577,22 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -3609,27 +3609,27 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -3644,42 +3644,42 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
-        </is>
-      </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3696,32 +3696,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3731,27 +3731,27 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3761,19 +3761,19 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3783,27 +3783,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3870,47 +3870,47 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3920,34 +3920,34 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
+          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3957,84 +3957,84 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4044,27 +4044,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>Rue Sewell (H2W 1V9)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -4089,39 +4089,39 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4131,27 +4131,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4161,54 +4161,54 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4218,27 +4218,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Appartement 2 chambres fermées, 974 pi², balcon – Plateau (Gilford/Chambord)</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 3L2, coin Gilford/Chambord)</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -4248,22 +4248,22 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Laurier</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4273,22 +4273,22 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-2-chambre-plateau-mont-royal/1739725006</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-jardin lumineux, sdb rénovée 2021, cuisine rénovée 2019, tous électros inclus + laveuse-sécheuse, à 2 min de l'avenue Mont-Royal, près parcs Lafontaine et Laurier, animaux limités, dispo 1er juillet ou août 2026</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/83/83da6eb9-3422-4702-b436-ed820032998c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4305,84 +4305,84 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>oui (petit balcon cuisine)</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Laurier</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Préfontaine</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4392,22 +4392,22 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
@@ -4447,29 +4447,29 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -4489,74 +4489,70 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>Jarry ou Crémazie</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4566,27 +4562,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>6904 Rue Hutchison, Montréal</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -4601,7 +4597,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Parc ou Acadie</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -4611,39 +4607,39 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4653,27 +4649,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
+          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
+          <t>5342 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4683,22 +4679,22 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6 (estimé)</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -4708,29 +4704,29 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
+          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4740,22 +4736,22 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
+          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
+          <t>3514 Avenue De Lorimier, Montréal</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -4765,7 +4761,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4775,49 +4771,49 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
+          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -4827,27 +4823,27 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
+          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Rue Sewell (H2W 1V9)</t>
+          <t>6904, 23e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -4857,12 +4853,12 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (terrasse sur le toit)</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien ou Rosemont (à vérifier)</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -4872,32 +4868,32 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -4914,22 +4910,22 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
+          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
+          <t>n/d (Montréal, QC H2R)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -4944,12 +4940,12 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -4959,7 +4955,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -4969,29 +4965,29 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
+          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -5001,27 +4997,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -5031,22 +5027,22 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
@@ -5056,29 +5052,29 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -5088,17 +5084,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -5108,64 +5104,64 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5175,22 +5171,22 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>1478 rue Dézéry</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5200,17 +5196,17 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -5220,39 +5216,39 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -5262,17 +5258,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -5282,22 +5278,22 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -5307,35 +5303,39 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q56" s="5" t="inlineStr"/>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R)</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
       <c r="Q57" s="5" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -5432,62 +5432,62 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -5497,19 +5497,19 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
+          <t>2121 Avenue Papineau, app. 106, Montréal</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11 (estimé)</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
@@ -5574,29 +5574,29 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
+          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>1478 rue Dézéry</t>
+          <t>6525 Rue Fabre, app. 2, Montréal</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5631,52 +5631,52 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>Préfontaine</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -5693,32 +5693,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+          <t>3855 rue St-André (H2L 3V9)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, stationnement, patio – Plateau</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -5790,74 +5790,74 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2181A Rue Marie-Anne, Montréal, QC H2H 1M9</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>oui (patio arrière)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-plateau-avec-stationnement-2-chambres-renove/1739130207</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Non chauffé, animaux limités, stationnement privé inclus, planchers bois franc, libre 15 juillet 2026</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2e8a22d5-2d29-437c-bd2c-a9be0878ff77?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5867,42 +5867,42 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
@@ -5954,27 +5954,27 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -5989,17 +5989,17 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
@@ -6009,29 +6009,29 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6066,59 +6066,59 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>Sherbrooke</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -6128,22 +6128,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>6391 Avenue Henri-Julien, Montréal</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -6153,59 +6153,59 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N66" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
         </is>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -6215,22 +6215,22 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>Rue Beaubien (Montréal, QC)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6240,52 +6240,52 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>12 (estimé)</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
-        </is>
-      </c>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
         </is>
       </c>
     </row>
@@ -6302,22 +6302,22 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>1889 Rue des Carrières, Montréal</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6337,49 +6337,49 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Rue Beaubien (Montréal, QC)</t>
+          <t>n/d (Montréal, QC)</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
@@ -6444,29 +6444,29 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
         </is>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>1889 Rue des Carrières, Montréal</t>
+          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Pie-IX (mentionné dans le titre)</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -6526,32 +6526,206 @@
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Location 4 et demi Plateau, pet friendly</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 Rosemont avec cour privée</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q72" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q70"/>
+  <autoFilter ref="A1:Q72"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -6622,6 +6796,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -576,22 +576,22 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
+          <t>Joli 7½ (3 chambres), terrasse et cour - à 5 min du métro Joliette (Hochelaga)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Villeray (adresse exacte n/d), Montréal</t>
+          <t>n/d (Montréal, QC H1W 3C5)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -631,29 +631,29 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-7-lumineux-avec-terrasse-et-cour-a-5-min-metro-joliette/1740607211</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
+          <t>Rez-de-chaussée avec étage, balcon + grande terrasse arrière et cabanon, 1 stationnement inclus, lave-vaisselle et laveuse-sécheuse inclus, meubles disponibles au besoin, animaux acceptés sous conditions, bail au mois possible, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/51/51601618-bdf1-4776-88b2-c87738ad33ef?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -663,84 +663,84 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
+          <t>5½ rénové 3 chambres, 1085 pi² - avenue d'Orléans (Hochelaga), près métro Joliette</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>8360 Rue Saint-Denis, Montréal</t>
+          <t>2435 Avenue d'Orléans, Montréal, QC H1W 3S3</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-a-louer-un-beau-5-1-2-de-3-chambres-fermees-avec-garage/1736086864</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
+          <t>Rez-de-chaussée d'un triplex, 1 stationnement privé inclus, accès cour arrière, non meublé, pas d'animaux, dispo 1er juillet 2026, à 450 m (~5 min) du métro Joliette et 600 m (~7 min) de Pie-IX</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/03/03d8944a-7b26-4350-b716-ca7ec27241fb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -750,84 +750,84 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
+          <t>5½ rénové 1000 pi², cour privée exclusive - boulevard Rosemont</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7186 Rue d'Iberville, Montréal</t>
+          <t>n/d (Boul. Rosemont, Montréal, QC H1Y 1M5)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Rosemont (à vérifier, adresse exacte non précisée)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-rosemont-la-petite-patrie/1740125612</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
+          <t>Entièrement rénové, climatisation incluse, cour privée exclusive aux locataires, animaux (chiens) acceptés, aucun stationnement inclus, bail 1 an, dispo 1er août 2026, distance au métro incertaine (adresse précise non indiquée dans l'annonce)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f6/f6ba5694-b433-4ed1-9bc1-e245d25714b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
+          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -847,154 +847,154 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7639 Rue Saint-Hubert, Montréal</t>
+          <t>8325B Rue Foucher, Montréal</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1414 Rue Villeray, app. 105, Montréal</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Fabre</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>bleue</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Jean-Talon ou Jarry (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5 (estimé)</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -1011,32 +1011,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1046,49 +1046,49 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Crémazie</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+          <t>Villeray (adresse exacte n/d), Montréal</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -1163,19 +1163,19 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1185,27 +1185,27 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 1M3</t>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Crémazie</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -1250,19 +1250,19 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
         </is>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1272,27 +1272,27 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>4224 Rue de Bellechasse, Montréal</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1394,42 +1394,42 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Fabre (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
+          <t>8360 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1568,27 +1568,27 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2 (estimé)</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -1598,19 +1598,19 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1620,32 +1620,32 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+          <t>4224 Rue de Bellechasse, Montréal</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1655,27 +1655,27 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Fabre (à vérifier)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1685,19 +1685,19 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1772,19 +1772,19 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1794,32 +1794,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1829,17 +1829,17 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -1946,19 +1946,19 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2033,19 +2033,19 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2065,22 +2065,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2090,27 +2090,27 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2120,15 +2120,19 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr"/>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2138,27 +2142,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2173,7 +2177,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -2183,17 +2187,17 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2203,15 +2207,19 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr"/>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2221,22 +2229,22 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2256,7 +2264,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -2266,7 +2274,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -2276,7 +2284,7 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2286,19 +2294,19 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2308,27 +2316,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2353,7 +2361,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2363,7 +2371,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2373,7 +2381,7 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr"/>
@@ -2381,7 +2389,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2391,32 +2399,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2426,27 +2434,27 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2456,19 +2464,15 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2478,27 +2482,27 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2508,22 +2512,22 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2533,7 +2537,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2543,12 +2547,12 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2565,32 +2569,32 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2600,27 +2604,27 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2630,14 +2634,10 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2652,27 +2652,27 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2682,32 +2682,32 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2717,19 +2717,19 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>3528 Avenue Coloniale, Montréal</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2871,39 +2871,39 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2913,27 +2913,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud/Village)</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Papineau ou Beaudry</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2958,39 +2958,39 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -3000,27 +3000,27 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -3035,49 +3035,49 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3087,22 +3087,22 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
+          <t>7186 Rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3122,27 +3122,27 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
@@ -3152,19 +3152,19 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,62 +3174,62 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+          <t>3528 Avenue Coloniale, Montréal</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3239,19 +3239,19 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
+          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -3296,27 +3296,27 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Papineau ou Beaudry</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3326,19 +3326,19 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3383,27 +3383,27 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3413,19 +3413,19 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3435,27 +3435,27 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -3470,27 +3470,27 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -3500,19 +3500,19 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3522,27 +3522,27 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
         </is>
       </c>
     </row>
@@ -3609,32 +3609,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3644,17 +3644,17 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
@@ -3674,19 +3674,19 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Crémazie</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -3783,27 +3783,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -3848,19 +3848,19 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
@@ -3947,7 +3947,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3992,42 +3992,42 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4044,27 +4044,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Rue Sewell (H2W 1V9)</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -4089,39 +4089,39 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4131,27 +4131,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -4186,29 +4186,29 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4218,32 +4218,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>7639 Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -4253,27 +4253,27 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jean-Talon ou Jarry (à vérifier)</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
@@ -4283,19 +4283,19 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -4335,32 +4335,32 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -4370,19 +4370,19 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4392,22 +4392,22 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4417,37 +4417,37 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -4457,19 +4457,19 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4479,42 +4479,42 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>Rue Sewell (H2W 1V9)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -4544,15 +4544,19 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="inlineStr"/>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4562,27 +4566,27 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>6904 Rue Hutchison, Montréal</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -4592,12 +4596,12 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Parc ou Acadie</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -4607,39 +4611,39 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4649,27 +4653,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>5342 Rue Saint-Denis, Montréal</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4684,49 +4688,49 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4736,7 +4740,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -4746,17 +4750,17 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>3514 Avenue De Lorimier, Montréal</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -4766,12 +4770,12 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (à vérifier)</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -4781,39 +4785,39 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -4823,7 +4827,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -4833,12 +4837,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>6904, 23e Avenue, Montréal</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -4853,17 +4857,17 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse sur le toit)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -4873,34 +4877,34 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4910,7 +4914,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -4920,74 +4924,70 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R)</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
-        </is>
-      </c>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -4997,22 +4997,22 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
+          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
+          <t>6904 Rue Hutchison, Montréal</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Parc ou Acadie</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -5042,17 +5042,17 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -5062,19 +5062,19 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
+          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -5084,32 +5084,32 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
+          <t>5342 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -5119,49 +5119,49 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
+          <t>6 (estimé)</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N54" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5171,22 +5171,22 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>1478 rue Dézéry</t>
+          <t>3514 Avenue De Lorimier, Montréal</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -5196,37 +5196,37 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
@@ -5236,19 +5236,19 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -5258,27 +5258,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+          <t>6904, 23e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (terrasse sur le toit)</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Beaubien ou Rosemont (à vérifier)</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -5303,17 +5303,17 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -5323,19 +5323,19 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
         </is>
       </c>
       <c r="Q56" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>n/d (Montréal, QC H2R)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
         </is>
       </c>
       <c r="Q57" s="5" t="inlineStr">
@@ -5422,7 +5422,7 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -5432,62 +5432,62 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -5497,19 +5497,19 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
         </is>
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>2121 Avenue Papineau, app. 106, Montréal</t>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
@@ -5574,29 +5574,29 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>6525 Rue Fabre, app. 2, Montréal</t>
+          <t>1478 rue Dézéry</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -5641,42 +5641,42 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Beaubien (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
         </is>
       </c>
     </row>
@@ -5693,32 +5693,32 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
         </is>
       </c>
     </row>
@@ -5780,42 +5780,42 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -5825,39 +5825,39 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5867,27 +5867,27 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -5902,17 +5902,17 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
@@ -5922,29 +5922,29 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5954,22 +5954,22 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>2121 Avenue Papineau, app. 106, Montréal</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -5989,27 +5989,27 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>11 (estimé)</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
         </is>
       </c>
     </row>
@@ -6041,22 +6041,22 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
+          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
+          <t>6525 Rue Fabre, app. 2, Montréal</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien (à vérifier)</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -6086,39 +6086,39 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
+          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -6128,22 +6128,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>6391 Avenue Henri-Julien, Montréal</t>
+          <t>3855 rue St-André (H2L 3V9)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -6163,49 +6163,49 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon (à vérifier)</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -6215,22 +6215,22 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Rue Beaubien (Montréal, QC)</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -6260,39 +6260,39 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6302,22 +6302,22 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>1889 Rue des Carrières, Montréal</t>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -6337,49 +6337,49 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -6424,42 +6424,42 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
@@ -6476,22 +6476,22 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -6511,42 +6511,42 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (mentionné dans le titre)</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
         </is>
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -6563,22 +6563,22 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Location 4 et demi Plateau, pet friendly</t>
+          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>6391 Avenue Henri-Julien, Montréal</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6598,134 +6598,569 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jean-Talon (à vérifier)</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange/bleue</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
         </is>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Rue Beaubien (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q72" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>1889 Rue des Carrières, Montréal</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+        </is>
+      </c>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>vu</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+        </is>
+      </c>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+        </is>
+      </c>
+      <c r="Q74" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Pie-IX (mentionné dans le titre)</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q75" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Location 4 et demi Plateau, pet friendly</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q76" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>5 1/2 Rosemont avec cour privée</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC)</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>2215</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L72" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N77" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
         </is>
       </c>
-      <c r="O72" s="5" t="inlineStr">
+      <c r="O77" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P72" s="6" t="inlineStr">
+      <c r="P77" s="6" t="inlineStr">
         <is>
           <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
-      <c r="Q72" s="5" t="inlineStr">
+      <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q72"/>
+  <autoFilter ref="A1:Q77"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -6798,6 +7233,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -576,27 +576,27 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Joli 7½ (3 chambres), terrasse et cour - à 5 min du métro Joliette (Hochelaga)</t>
+          <t>5½ (3 chambres fermées), 1100 pi² - Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3C5)</t>
+          <t>3984, rue De Bullion, Montréal (H2W 2E4)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -631,22 +631,22 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-7-lumineux-avec-terrasse-et-cour-a-5-min-metro-joliette/1740607211</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-au-plateau-three-3-bedroom-apartment-in-plateau/1740633307</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée avec étage, balcon + grande terrasse arrière et cabanon, 1 stationnement inclus, lave-vaisselle et laveuse-sécheuse inclus, meubles disponibles au besoin, animaux acceptés sous conditions, bail au mois possible, dispo 1er août 2026</t>
+          <t>Chauffage électrique non inclus, animaux acceptés, planchers bois franc, électroménagers inclus, dispo 1er août 2026 (bail 1 an)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/51/51601618-bdf1-4776-88b2-c87738ad33ef?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/64/64cccc9c-2b44-43ab-bc78-5ef6a4df00f6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -663,27 +663,27 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>5½ rénové 3 chambres, 1085 pi² - avenue d'Orléans (Hochelaga), près métro Joliette</t>
+          <t>Grand 6½ (3 chambres), 2 balcons, à 3 min du métro Jarry - Villeray</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2435 Avenue d'Orléans, Montréal, QC H1W 3S3</t>
+          <t>n/d (Montréal, QC H2R 2E8, 2e étage)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -718,22 +718,22 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-a-louer-un-beau-5-1-2-de-3-chambres-fermees-avec-garage/1736086864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740626046</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée d'un triplex, 1 stationnement privé inclus, accès cour arrière, non meublé, pas d'animaux, dispo 1er juillet 2026, à 450 m (~5 min) du métro Joliette et 600 m (~7 min) de Pie-IX</t>
+          <t>Dispo 1er août 2026, non-fumeur, animaux non permis, lave-vaisselle/frigo inclus, laveuse-sécheuse dans l'unité, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/03/03d8944a-7b26-4350-b716-ca7ec27241fb?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/46/46364391-a0b3-4fdb-9a03-1b6d1cac4468?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>5½ rénové 1000 pi², cour privée exclusive - boulevard Rosemont</t>
+          <t>6½ lumineux, 3 chambres fermées, rénové et équipé - Rosemont</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>n/d (Boul. Rosemont, Montréal, QC H1Y 1M5)</t>
+          <t>5838, avenue Louis-Hébert, Montréal</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Rosemont (à vérifier, adresse exacte non précisée)</t>
+          <t>Rosemont ou Beaubien (à vérifier)</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -805,22 +805,22 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-rosemont-la-petite-patrie/1740125612</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-lumineux-3-ch-fermees-renove-equipe-rosemont/1740407731</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Entièrement rénové, climatisation incluse, cour privée exclusive aux locataires, animaux (chiens) acceptés, aucun stationnement inclus, bail 1 an, dispo 1er août 2026, distance au métro incertaine (adresse précise non indiquée dans l'annonce)</t>
+          <t>Sous-location jusqu'au 31 juillet 2027, dispo 11 juillet 2026, 2 thermopompes (chauffage/clim), électroménagers neufs, animaux limités</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f6/f6ba5694-b433-4ed1-9bc1-e245d25714b2?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/55/5508505f-2676-403c-a0ef-0ff508313938?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -837,27 +837,27 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
+          <t>Condo 4½ semi-meublé face au parc Père-Marquette - Rosemont</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8325B Rue Foucher, Montréal</t>
+          <t>n/d (face au parc Père-Marquette, Montréal)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>970</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non (terrasse commune sur le toit)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-dans-rosemont-la-petite-patrie/1739545131</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
+          <t>Semi-meublé, buanderie privée, lave-vaisselle, climatisation, rangement au sous-sol, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c32bb989-3256-4fd9-b5c7-30a77bfd8b2b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -924,22 +924,22 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
+          <t>4 chambres meublé, Plateau-Mont-Royal (Marketplace)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1414 Rue Villeray, app. 105, Montréal</t>
+          <t>3681, avenue Coloniale, Montréal (H2X 2Y7)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -949,233 +949,233 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Mont-Royal ou Sherbrooke (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1578661203923320</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Meublé, orienté étudiants, bail 1 an, dispo maintenant. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/746058480_2385279625296639_1965210297754561149_n.jpg?stp=c93.0.895.895a_dst-jpg_tt6&amp;cstp=mx895x895&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ngElLDKbnLQQ7kNvwHndFuc&amp;_nc_oc=AdpOYEcvWwImdnqaiYyy1pwfVcV2sab1mFRQ5KYGa5FE_CkYORsBa8yvv6PCL2lbQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EorVHkPe0HNRZxtO75C5fg&amp;_nc_ss=7f2a8&amp;oh=00_AQBlE2b8WT_3jlX6ddiFysYujtaCjsMiZRfF96JJT7pp3g&amp;oe=6A60805A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Cession de bail 7½, Rosemont-La Petite-Patrie (Marketplace)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H2G 1T5)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1375157431101110</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Cession de bail. Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702670571_1710902896599779_1133264177050399379_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=akFqSvK3rfAQ7kNvwG-Cqey&amp;_nc_oc=Adrp5N9Rg13Pf-obfNZqB1ZqwyOcgjJji8vk0ggvRJiA9uCo-xDJXuQAit6O7YIGPW0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQBG56r36JKH2gkm4Baddcm0ylaFria-4p9Il0vYABnyMg&amp;oe=6A607060</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Beau 5½ à Nouveau Rosemont (Marketplace)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur Nouveau-Rosemont, Montréal)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Fabre</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Villeray (adresse exacte n/d), Montréal</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Fabre</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/771126382598215</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/674573089_942123441857660_1258864760862245194_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=-PqFDWdPNa8Q7kNvwG9FoYC&amp;_nc_oc=Adqy82S_lfHjbp4dkLyXqO9W2nrNBD-zKhYTIwlodmCwj46lhM9QhEG2rupuBRJOPVI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQDV5R2cb2f6avoKzX1khDbQ_SvUKiySFkJsux9T10Rmdg&amp;oe=6A6059BA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1185,32 +1185,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
+          <t>Joli 7½ (3 chambres), terrasse et cour - à 5 min du métro Joliette (Hochelaga)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
+          <t>n/d (Montréal, QC H1W 3C5)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1220,17 +1220,17 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Crémazie</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1240,29 +1240,29 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-7-lumineux-avec-terrasse-et-cour-a-5-min-metro-joliette/1740607211</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
+          <t>Rez-de-chaussée avec étage, balcon + grande terrasse arrière et cabanon, 1 stationnement inclus, lave-vaisselle et laveuse-sécheuse inclus, meubles disponibles au besoin, animaux acceptés sous conditions, bail au mois possible, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/51/51601618-bdf1-4776-88b2-c87738ad33ef?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1272,27 +1272,27 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1307,49 +1307,49 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
+          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 1M3</t>
+          <t>Villeray (adresse exacte n/d), Montréal</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
         </is>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1446,54 +1446,54 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Crémazie</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Kijiji</t>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
         </is>
       </c>
       <c r="O12" s="5" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1543,22 +1543,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>8360 Rue Saint-Denis, Montréal</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1578,39 +1578,39 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1620,32 +1620,32 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>4224 Rue de Bellechasse, Montréal</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1655,42 +1655,42 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Fabre (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -1707,22 +1707,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1762,29 +1762,29 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1794,27 +1794,27 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
+          <t>8360 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1829,27 +1829,27 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>2 (estimé)</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1881,32 +1881,32 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+          <t>4224 Rue de Bellechasse, Montréal</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1916,27 +1916,27 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Fabre (à vérifier)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -1946,19 +1946,19 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1968,32 +1968,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2033,19 +2033,19 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2055,32 +2055,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2120,19 +2120,19 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2142,27 +2142,27 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2207,19 +2207,19 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2259,22 +2259,22 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2294,19 +2294,19 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2326,22 +2326,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2351,27 +2351,27 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2381,15 +2381,19 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q22" s="5" t="inlineStr"/>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2399,27 +2403,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2444,17 +2448,17 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2464,15 +2468,19 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr"/>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2482,22 +2490,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2517,7 +2525,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2527,7 +2535,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2537,7 +2545,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2547,19 +2555,19 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2569,27 +2577,27 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2614,7 +2622,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2624,7 +2632,7 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2634,7 +2642,7 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr"/>
@@ -2642,7 +2650,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2652,32 +2660,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2687,27 +2695,27 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -2717,19 +2725,15 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2739,27 +2743,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2769,22 +2773,22 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2794,7 +2798,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2804,12 +2808,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2826,32 +2830,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2861,27 +2865,27 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2891,14 +2895,10 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2913,27 +2913,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2943,32 +2943,32 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
@@ -2978,19 +2978,19 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -3000,22 +3000,22 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
@@ -3065,19 +3065,19 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3087,32 +3087,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>7186 Rue d'Iberville, Montréal</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3122,49 +3122,49 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,84 +3174,84 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>3528 Avenue Coloniale, Montréal</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3261,27 +3261,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud/Village)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -3296,49 +3296,49 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Papineau ou Beaudry</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>5½ rénové 3 chambres, 1085 pi² - avenue d'Orléans (Hochelaga), près métro Joliette</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
+          <t>2435 Avenue d'Orléans, Montréal, QC H1W 3S3</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -3393,17 +3393,17 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-a-louer-un-beau-5-1-2-de-3-chambres-fermees-avec-garage/1736086864</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3413,19 +3413,19 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
+          <t>Rez-de-chaussée d'un triplex, 1 stationnement privé inclus, accès cour arrière, non meublé, pas d'animaux, dispo 1er juillet 2026, à 450 m (~5 min) du métro Joliette et 600 m (~7 min) de Pie-IX</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/03/03d8944a-7b26-4350-b716-ca7ec27241fb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3435,22 +3435,22 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
+          <t>7186 Rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3470,27 +3470,27 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -3500,19 +3500,19 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3522,62 +3522,62 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+          <t>3528 Avenue Coloniale, Montréal</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -3587,19 +3587,19 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
+          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3644,27 +3644,27 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Papineau ou Beaudry</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
@@ -3674,19 +3674,19 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3696,32 +3696,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3731,27 +3731,27 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -3761,19 +3761,19 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3783,27 +3783,27 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -3848,19 +3848,19 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3870,27 +3870,27 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -3900,17 +3900,17 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
         </is>
       </c>
     </row>
@@ -3957,32 +3957,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
@@ -4022,19 +4022,19 @@
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4044,27 +4044,27 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Crémazie</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -4089,17 +4089,17 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4131,27 +4131,27 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -4166,27 +4166,27 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -4218,27 +4218,27 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>7639 Rue Saint-Hubert, Montréal</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -4248,54 +4248,54 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon ou Jarry (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -4355,27 +4355,27 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -4402,22 +4402,22 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -4427,49 +4427,49 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4479,27 +4479,27 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Rue Sewell (H2W 1V9)</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -4529,34 +4529,34 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4566,22 +4566,22 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
+          <t>5½ rénové 1000 pi², cour privée exclusive - boulevard Rosemont</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
+          <t>n/d (Boul. Rosemont, Montréal, QC H1Y 1M5)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Rosemont (à vérifier, adresse exacte non précisée)</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-rosemont-la-petite-patrie/1740125612</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -4631,19 +4631,19 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
+          <t>Entièrement rénové, climatisation incluse, cour privée exclusive aux locataires, animaux (chiens) acceptés, aucun stationnement inclus, bail 1 an, dispo 1er août 2026, distance au métro incertaine (adresse précise non indiquée dans l'annonce)</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f6/f6ba5694-b433-4ed1-9bc1-e245d25714b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>7639 Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jean-Talon ou Jarry (à vérifier)</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -4718,19 +4718,19 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -4740,27 +4740,27 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -4805,19 +4805,19 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -4827,22 +4827,22 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -4852,37 +4852,37 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -4892,19 +4892,19 @@
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4914,42 +4914,42 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>Rue Sewell (H2W 1V9)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
@@ -4979,15 +4979,19 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q52" s="5" t="inlineStr"/>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -4997,27 +5001,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>6904 Rue Hutchison, Montréal</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -5027,12 +5031,12 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Parc ou Acadie</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -5042,39 +5046,39 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -5084,27 +5088,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>5342 Rue Saint-Denis, Montréal</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -5119,49 +5123,49 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5171,7 +5175,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -5181,17 +5185,17 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>3514 Avenue De Lorimier, Montréal</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -5201,12 +5205,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (à vérifier)</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -5216,39 +5220,39 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -5258,7 +5262,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -5268,12 +5272,12 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>6904, 23e Avenue, Montréal</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5288,17 +5292,17 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse sur le toit)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont (à vérifier)</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -5308,34 +5312,34 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q56" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5345,7 +5349,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -5355,74 +5359,70 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R)</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
-        </is>
-      </c>
-      <c r="Q57" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -5432,22 +5432,22 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Condo 4 1/2, terrasse sur le toit - coin Rachel/St-Dominique, 8 min du métro Mont-Royal</t>
+          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>267 Rue Rachel Est, Montréal, QC H2W 1E5</t>
+          <t>8325B Rue Foucher, Montréal</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -5477,17 +5477,17 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-plateau-mont-royal/1739033791</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -5497,19 +5497,19 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Terrasse sur le toit, disponible 15 juin 2026, superficie non précisée dans l'annonce</t>
+          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/29/2918495a-3b7e-4afa-af2d-bc65af9d15a1?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -5519,22 +5519,22 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
+          <t>6904 Rue Hutchison, Montréal</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5544,22 +5544,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Parc ou Acadie</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
@@ -5584,19 +5584,19 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
         </is>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>1478 rue Dézéry</t>
+          <t>5342 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -5641,27 +5641,27 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 (estimé)</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -5693,27 +5693,27 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+          <t>3514 Avenue De Lorimier, Montréal</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
@@ -5758,19 +5758,19 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -5780,27 +5780,27 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>6904, 23e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui (terrasse sur le toit)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Beaubien ou Rosemont (à vérifier)</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -5825,39 +5825,39 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N62" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
-        </is>
-      </c>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
         </is>
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5867,62 +5867,62 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>n/d (Montréal, QC H2R)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
@@ -5932,19 +5932,19 @@
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
         </is>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2121 Avenue Papineau, app. 106, Montréal</t>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>11 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
@@ -6009,29 +6009,29 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
+          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -6041,22 +6041,22 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
+          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>6525 Rue Fabre, app. 2, Montréal</t>
+          <t>1478 rue Dézéry</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -6076,42 +6076,42 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Beaubien (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
+          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
         </is>
       </c>
     </row>
@@ -6128,32 +6128,32 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>Rue Drolet entre St-Zotique et Bélanger</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
@@ -6183,22 +6183,22 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
         </is>
       </c>
     </row>
@@ -6215,42 +6215,42 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -6260,39 +6260,39 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
         </is>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6302,27 +6302,27 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>5472 1ere Avenue, Montréal</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>995</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -6337,17 +6337,17 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
@@ -6357,29 +6357,29 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>2121 Avenue Papineau, app. 106, Montréal</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -6424,27 +6424,27 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>11 (estimé)</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
         </is>
       </c>
     </row>
@@ -6476,22 +6476,22 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
+          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
+          <t>6525 Rue Fabre, app. 2, Montréal</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Beaubien (à vérifier)</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -6521,39 +6521,39 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N70" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
-        </is>
-      </c>
-      <c r="O70" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
+          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
         </is>
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6563,22 +6563,22 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>6391 Avenue Henri-Julien, Montréal</t>
+          <t>3855 rue St-André (H2L 3V9)</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -6598,49 +6598,49 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon (à vérifier)</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
+          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Rue Beaubien (Montréal, QC)</t>
+          <t>4275 Rue de Bordeaux, Montréal</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -6695,39 +6695,39 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
         </is>
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -6737,22 +6737,22 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>1889 Rue des Carrières, Montréal</t>
+          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -6772,49 +6772,49 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Mont-Royal ou Papineau (à vérifier)</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
         </is>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -6824,22 +6824,22 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>62 rue Rachel Est, Montréal</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -6859,49 +6859,49 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
         </is>
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -6911,22 +6911,22 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+          <t>1414 Rue Villeray, app. 105, Montréal</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -6946,42 +6946,42 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX (mentionné dans le titre)</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Location 4 et demi Plateau, pet friendly</t>
+          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC)</t>
+          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -7033,42 +7033,42 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
         </is>
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -7085,82 +7085,604 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
+          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>6391 Avenue Henri-Julien, Montréal</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>8 (estimé)</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+        </is>
+      </c>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Meublé, finitions haut de gamme, pas d'animaux, Walk Score 98, proche marché Jean-Talon et cafés/restos, dispo 1er juin 2026, distance au métro estimée</t>
+        </is>
+      </c>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADB62FFDDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Superbe 2 chambres rénové, rue Beaubien - Petite-Italie</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Rue Beaubien (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2219881575422253</t>
+        </is>
+      </c>
+      <c r="O78" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Entièrement rénové, cour arrière privée, Walk Score 99, à quelques pas de cafés/restos/boulangeries/épiceries fines de la Petite-Italie, à environ 10 min du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q78" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/714823210_969706739294886_222709070726311984_n.jpg?stp=c134.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=Q4rmFfALvM0Q7kNvwH2W42u&amp;_nc_oc=AdpINKj09PPc8Re8DxGgY3chRB5RnttQl9NAS-AFL9O8KTqqt1dR9NYx_1WNt0O8lww&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=JqfxygLQ7LNnSdbCmwTgsw&amp;_nc_ss=7f2a8&amp;oh=00_AQDsARrJ7YHo6O-8Zg1v5X3ykFLojfdUxVqQy1Z7t2iyQg&amp;oe=6A5DC11E</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 (avec sous-sol), 2 garages – Rosemont</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>1889 Rue des Carrières, Montréal</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>Centris</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-rosemont-la-petite-patrie/15047676</t>
+        </is>
+      </c>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Walk Score 94, 2 places de garage à 250$/mois chacune, rénovations récentes sous-sol et salle de bain, libre 5 jours après acceptation du bail</t>
+        </is>
+      </c>
+      <c r="Q79" s="5" t="inlineStr">
+        <is>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE603764DDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>5-1/2 Rosemont (La Petite-Patrie)</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/1249775127316090</t>
+        </is>
+      </c>
+      <c r="O80" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper. Lien Facebook (connexion requise) pour plus de détails</t>
+        </is>
+      </c>
+      <c r="Q80" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/671899528_1686294965723943_4545041476511987210_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=xqmMQDvhJyAQ7kNvwH2BiIA&amp;_nc_oc=Adrb6HhJ7AWRb5Vln_jWCEMjozYYhefbdIyqNV0qQcHSggRpyTjrMcklU7eB9de9Y0s&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=POnFrCwMzHXIAMbS8hYJRQ&amp;_nc_ss=7f2a8&amp;oh=00_AQBeKgxbGCX6t2QjecZXjpQL0PuubZ84LadG2I8Gj_1mug&amp;oe=6A5E87C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>5 1/2 lumineux à Rosemont - 2 chambres - Masson / Pie-IX</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>n/d (secteur Masson / Pie-IX, Montréal)</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Pie-IX (mentionné dans le titre)</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/2238212030311408</t>
+        </is>
+      </c>
+      <c r="O81" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement, description non disponible via le scraper ; secteur Masson/Pie-IX mentionné dans le titre mais distance exacte inconnue. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q81" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/719804341_36311671888447568_3859659500532179340_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=vtlzBRqRSRoQ7kNvwHzTYPO&amp;_nc_oc=AdoFOL6FWNc1M9UybWVnYuEzJQJlAq6neF5rbnVhe9_6oLH2S29hP6IEKy2E7BpCLDg&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQB2Z-K5zeotniKSOg35MSVtER8_xPmH2m9kSVj-TPJ32A&amp;oe=6A5E8CF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Location 4 et demi Plateau, pet friendly</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC)</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/marketplace/item/880670661257255</t>
+        </is>
+      </c>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Annonce titre seulement (prix affiché entre 2150$ et 2350$), description non disponible via le scraper, animaux acceptés. Lien Facebook (connexion requise)</t>
+        </is>
+      </c>
+      <c r="Q82" s="5" t="inlineStr">
+        <is>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/739200097_2136278627323814_3520943268052786943_n.jpg?stp=c90.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=gPcahdqySPYQ7kNvwGsYlqA&amp;_nc_oc=Adr3EDMhZojMTr_b6P1fzAVXVarO60w-XBK6dTJaEUmqMft4FzmSbchZ5AfV6DC3Usw&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQBgwOGHm1ihFR3tvhrAE6VDaZym-txS_aF6xIBAwy5A1Q&amp;oe=6A5EA1A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>vu</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
           <t>5 1/2 Rosemont avec cour privée</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>n/d (Montréal, QC)</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
         <is>
           <t>2215</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="N77" s="7" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/marketplace/item/1493110625829174</t>
         </is>
       </c>
-      <c r="O77" s="5" t="inlineStr">
+      <c r="O83" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P77" s="6" t="inlineStr">
+      <c r="P83" s="6" t="inlineStr">
         <is>
           <t>Annonce titre seulement, description non disponible via le scraper ; cour privée mentionnée. Lien Facebook (connexion requise)</t>
         </is>
       </c>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730530074_1035539099460685_3801485303896565628_n.jpg?stp=c313.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=_9b7saLCWEUQ7kNvwHrw_2v&amp;_nc_oc=AdoqEj5UFxI4lgfrZP0kbf8mdi_MJO6fIO-zv3fvQ5DsX656NtR6Rf8AiVxw-oho-l4&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=qCpowFOKCzme7PAXiFpzMA&amp;_nc_ss=7f2a8&amp;oh=00_AQDqhmwAH6WdMqAuOtshO7wqRdBG7RkedN25_yaUpz5ikg&amp;oe=6A5EB662</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q77"/>
+  <autoFilter ref="A1:Q83"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -7238,6 +7760,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/annonces.xlsx
+++ b/annonces.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Annonces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Annonces'!$A$1:$Q$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -576,27 +576,27 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>5½ (3 chambres fermées), 1100 pi² - Plateau-Mont-Royal</t>
+          <t>3 chambres + bureau, meublé, 1 mois gratuit - Hochelaga, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>3984, rue De Bullion, Montréal (H2W 2E4)</t>
+          <t>n/d (Rue Hogan, Montréal, QC H2K 2T4)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Préfontaine ou Frontenac (à vérifier)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-au-plateau-three-3-bedroom-apartment-in-plateau/1740633307</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedrooms/1739807209</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -641,19 +641,19 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Chauffage électrique non inclus, animaux acceptés, planchers bois franc, électroménagers inclus, dispo 1er août 2026 (bail 1 an)</t>
+          <t>1 mois gratuit, meublé, animaux non admis</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/64/64cccc9c-2b44-43ab-bc78-5ef6a4df00f6?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/da/da7beded-654c-404a-b143-bda5b0555644?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Grand 6½ (3 chambres), 2 balcons, à 3 min du métro Jarry - Villeray</t>
+          <t>Grand logement 6½ tout rénové, 1350 pi², 2 balcons - coeur de Villeray, à 1 min du métro Jarry</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -673,22 +673,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R 2E8, 2e étage)</t>
+          <t>n/d (Montréal, QC H2P 2K6)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740626046</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-logement-6-1-2-au-coeur-de-villeray-tout-renove/1738688321</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -728,19 +728,19 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Dispo 1er août 2026, non-fumeur, animaux non permis, lave-vaisselle/frigo inclus, laveuse-sécheuse dans l'unité, prix à la limite haute du budget</t>
+          <t>Rénové, climatisation, laveuse-sécheuse incluse, dispo 15 juin 2026</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/46/46364391-a0b3-4fdb-9a03-1b6d1cac4468?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d043ccd7-f8fc-4b34-97cc-d3dbf9d62374?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -750,32 +750,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>6½ lumineux, 3 chambres fermées, rénové et équipé - Rosemont</t>
+          <t>Grand 4½ meublé, 2 chambres, à 5 min du métro Préfontaine - Hochelaga</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5838, avenue Louis-Hébert, Montréal</t>
+          <t>n/d (Rue Dézéry, Montréal, QC H1W 2S2)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Rosemont ou Beaubien (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-lumineux-3-ch-fermees-renove-equipe-rosemont/1740407731</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-meuble-metro-prefontaine-bail-6-mois/1739936806</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -815,19 +815,19 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Sous-location jusqu'au 31 juillet 2027, dispo 11 juillet 2026, 2 thermopompes (chauffage/clim), électroménagers neufs, animaux limités</t>
+          <t>Meublé, bail 6 mois possible, animaux limités</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/55/5508505f-2676-403c-a0ef-0ff508313938?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/27/2737d02c-077a-47e2-8476-d57ae185048f?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -837,42 +837,42 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Condo 4½ semi-meublé face au parc Père-Marquette - Rosemont</t>
+          <t>Appartement 6½, 2 balcons, stationnement inclus - rue Saint-Denis (Villeray)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>n/d (face au parc Père-Marquette, Montréal)</t>
+          <t>8188 Rue Saint-Denis, Montréal, QC H2P 2G6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>non (terrasse commune sur le toit)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -892,29 +892,29 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-dans-rosemont-la-petite-patrie/1739545131</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-6-1-2/1738696107</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Semi-meublé, buanderie privée, lave-vaisselle, climatisation, rangement au sous-sol, dispo 1er juillet 2026</t>
+          <t>Reprise de bail, stationnement inclus</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c32bb989-3256-4fd9-b5c7-30a77bfd8b2b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ba/bac95678-e0f1-49cb-85a0-042eb0c644ce?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -924,42 +924,42 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>4 chambres meublé, Plateau-Mont-Royal (Marketplace)</t>
+          <t>2 chambres meublé, grande terrasse 1500 pi² - près métro Fabre (Villeray)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3681, avenue Coloniale, Montréal (H2X 2Y7)</t>
+          <t>2110 Rue Tillemont, Montréal, QC H2E 1E3</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (grande terrasse ~25x30 pi)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Sherbrooke (à vérifier)</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -969,39 +969,39 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1578661203923320</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/2-chambre-metro-fabre/1738179989</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Meublé, orienté étudiants, bail 1 an, dispo maintenant. Lien Facebook (connexion requise)</t>
+          <t>Meublé, laveuse-sécheuse, dispo 31 mai 2026</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/746058480_2385279625296639_1965210297754561149_n.jpg?stp=c93.0.895.895a_dst-jpg_tt6&amp;cstp=mx895x895&amp;ctp=s565x565&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=ngElLDKbnLQQ7kNvwHndFuc&amp;_nc_oc=AdpOYEcvWwImdnqaiYyy1pwfVcV2sab1mFRQ5KYGa5FE_CkYORsBa8yvv6PCL2lbQ7E&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EorVHkPe0HNRZxtO75C5fg&amp;_nc_ss=7f2a8&amp;oh=00_AQBlE2b8WT_3jlX6ddiFysYujtaCjsMiZRfF96JJT7pp3g&amp;oe=6A60805A</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/e8/e837ddc1-807c-40ac-9da3-f5fabd7ec855?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Cession de bail 7½, Rosemont-La Petite-Patrie (Marketplace)</t>
+          <t>5½ rénové 1000 pi², eau incluse - La Petite-Patrie, près métro Fabre</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 1T5)</t>
+          <t>n/d (Montréal, QC H2G 2Y9)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1041,54 +1041,54 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1375157431101110</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer-5-1-2/1740736227</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Cession de bail. Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
+          <t>Eau incluse, climatisation, rénové, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702670571_1710902896599779_1133264177050399379_n.jpg?stp=c0.86.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=akFqSvK3rfAQ7kNvwG-Cqey&amp;_nc_oc=Adrp5N9Rg13Pf-obfNZqB1ZqwyOcgjJji8vk0ggvRJiA9uCo-xDJXuQAit6O7YIGPW0&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQBG56r36JKH2gkm4Baddcm0ylaFria-4p9Il0vYABnyMg&amp;oe=6A607060</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15c8766b-815b-40bf-b836-c2b5c5168deb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1098,867 +1098,867 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Beau 5½ à Nouveau Rosemont (Marketplace)</t>
+          <t>Beau 6½, 2 balcons, 900 pi² - La Petite-Patrie, près métro Beaubien</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Montréal, QC H2S 2P5, secteur Plaza St-Hubert)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>oui (2 balcons)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-a-louer-dans-petite-patrie-pres-du-metro-beaubien/1740568244</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Dispo 1er sept 2026, eau incluse, partiellement meublé, proche Plaza St-Hubert</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/60/60dcd8d4-6793-4105-ac1b-3f8753756a3c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Condo de coin meublé, 2 chambres, vue sur parc - Rosemont/Angus, près métro Joliette</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>n/d (secteur Nouveau-Rosemont, Montréal)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur Angus, Montréal, QC H1X 3J4, près rue Bélanger)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/771126382598215</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>oui (privé, vue sur parc)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/2-050-mois-condo-de-coin-meuble-de-2-chambres-rosemont-ang/1740664802</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Meublé, dispo 10 août 2026, chats acceptés</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cb/cb9f1258-ed1f-4e2f-abee-c7c7c2e85b60?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>4½ tout compris, 2 balcons, ~1184 pi² - Plateau (Marie-Anne/De La Roche)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur Marie-Anne / De La Roche, Montréal, QC H2J 3J2)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Peu de détails disponibles dans l'annonce (pas d'adresse exacte ni de superficie). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/674573089_942123441857660_1258864760862245194_n.jpg?stp=c89.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=109&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=-PqFDWdPNa8Q7kNvwG9FoYC&amp;_nc_oc=Adqy82S_lfHjbp4dkLyXqO9W2nrNBD-zKhYTIwlodmCwj46lhM9QhEG2rupuBRJOPVI&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=8ft2OWSslHjx1ccZ2nFb1w&amp;_nc_ss=7f2a8&amp;oh=00_AQDV5R2cb2f6avoKzX1khDbQ_SvUKiySFkJsux9T10Rmdg&amp;oe=6A6059BA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Joli 7½ (3 chambres), terrasse et cour - à 5 min du métro Joliette (Hochelaga)</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1W 3C5)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>oui (2 balcons)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mont-Royal</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/1er-octobre-4-1-2-tout-comprit-a-louer-sur-le-plateau-mont-royal/1740707852</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Tout inclus (chauffage, hydro, eau), meublé, dispo 1er oct 2026</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/fe/fe47e774-774a-42ad-8e56-86170263508b?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2BR condo 4½ prêt à emménager, balcons avant/arrière - Plateau (Saint-Louis)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur Saint-Louis, Montréal, QC H2X 2Y4)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>oui (avant et arrière)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Sherbrooke</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/2br-plateau-condo-4-1-2-move-in-ready/1733616523</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Non meublé, eau incluse, aucun animal, Walk Score 99, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/b8/b82d1714-bac1-4fea-83df-1e7a4854d51c?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>6½ lumineux, 2 chambres + bureau, 1125 pi² - rue Chambord (Rosemont), près métro Beaubien</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6565 Rue Chambord, Montréal</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>oui (avant et arrière)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Beaubien</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/6-1-2-a-louer/hab-6565-chambord-1132276</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>3e étage d'un triplex, dispo immédiatement (1er juillet), non-fumeurs, pas d'animaux, prix à la limite haute du budget</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132276/6-1-2-rosemont-petite-patrie-600-15660148.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Cession de bail - Grand 4½ meublé, dispo 1er sept - Villeray</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur parc Jarry, Montréal, QC H2R 2P8)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-4-meuble-a-villeray-dispo-1e-sept/1740575992</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Meublé, internet + hydro + 1 stationnement inclus, dispo 1er sept 2026</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/22/22a45f05-2998-4446-94bf-040ee3e94cff?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2 chambres meublé, chauffage/eau/hydro inclus - Villeray, près métro Jean-Talon</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>n/d (secteur parc Jarry, Montréal, QC H2R 2P8)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-7-lumineux-avec-terrasse-et-cour-a-5-min-metro-joliette/1740607211</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>Rez-de-chaussée avec étage, balcon + grande terrasse arrière et cabanon, 1 stationnement inclus, lave-vaisselle et laveuse-sécheuse inclus, meubles disponibles au besoin, animaux acceptés sous conditions, bail au mois possible, dispo 1er août 2026</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/51/51601618-bdf1-4776-88b2-c87738ad33ef?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Près du parc Lalancette (adresse exacte n/d)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/2-beds-1-bath-flat/1739031958</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Chauffage, eau et hydro inclus, bail 1 an</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/8e/8e90b51e-590e-45cb-9d6d-155aaf096480?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>5½ reprise de bail, walk-in/bureau, balcon arrière - rue Saint-Denis (Villeray)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Villeray</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>n/d (Rue Saint-Denis, Montréal, QC H2R 2E5)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>oui (arrière)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/51-2-reprise-de-bail-1er-juillet/1737970220</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Chats acceptés, non meublé, walk-in/bureau additionnel</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/87/870993c9-a899-49c5-b996-e9103fef0cc7?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Condo 2 chambres construit 2012, option tout inclus - Rosemont/La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont-La Petite-Patrie</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3320 Rue Dandurand, Montréal, QC H1X 1M6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Villeray (adresse exacte n/d), Montréal</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Fabre</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>10 (estimé)</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Rosemont</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Crémazie</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-2-chambres-2012-rosemont-petite-patrie-option-tout-iclus/1740633223</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Dispo 1er août 2026, option tout inclus (hydro, wifi), meublé</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/eb/eb078bfc-6406-4c44-aaea-a47152705a1b?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>NOUVEAU</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Condo 4½ clé en main, 2 balcons privés - Plateau/Mile-End</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Le Plateau-Mont-Royal</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5350 Rue Drolet, Montréal, QC H2T 2H4</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>oui (2 balcons privés)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Laurier ou Rosemont (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Kijiji</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Hochelaga-Maisonneuve</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Montréal, QC H1W 1M3</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2250</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Beaubien</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Kijiji</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Villeray</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>8360 Rue Saint-Denis, Montréal</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>2 (estimé)</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>vu</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Rosemont-La Petite-Patrie</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>4224 Rue de Bellechasse, Montréal</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Fabre (à vérifier)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>bleue</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>8 (estimé)</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-condo-4-cle-en-main-plateau-mile-end/1740380612</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Électros fournis, thermopompe, dispo 15 juillet 2026</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/f1/f1713eb8-b958-4345-9866-6f8f019186e1?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1968,32 +1968,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
+          <t>Joli 7½ (3 chambres), terrasse et cour - à 5 min du métro Joliette (Hochelaga)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>n/d (Montréal, QC H1W 3C5)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
@@ -2023,22 +2023,22 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/joli-7-lumineux-avec-terrasse-et-cour-a-5-min-metro-joliette/1740607211</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
+          <t>Rez-de-chaussée avec étage, balcon + grande terrasse arrière et cabanon, 1 stationnement inclus, lave-vaisselle et laveuse-sécheuse inclus, meubles disponibles au besoin, animaux acceptés sous conditions, bail au mois possible, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/51/51601618-bdf1-4776-88b2-c87738ad33ef?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
+          <t>5 1/2 rénové 3 chambres près métro Joliette (cession de bail)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2065,22 +2065,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1W 3N5)</t>
+          <t>Près du parc Lalancette (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Joliette ou Pie-IX</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -2100,39 +2100,39 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
+          <t>https://www.facebook.com/marketplace/item/1611452633675447</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
+          <t>Cession de bail. 1100 pi2 rénové, 3 grandes chambres fermées avec garde-robe dont une avec balcon, second balcon sur cour, locker au sous-sol, chauffage/eau chaude/wifi inclus. 5 min à pied du métro Joliette selon la fiche, dispo 1er août. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744782828_2425425677956674_6748123711102009567_n.jpg?stp=c0.123.1290.1290a_dst-jpg_tt6&amp;cstp=mx1290x1290&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=QyFHGQtYXmAQ7kNvwGAvYTo&amp;_nc_oc=Adq0n0QGekjLictcQqyNCD5OWzTZP-ByT68TnmMdUFrBRe8Gta7m-AQEhavEJDocpUc&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQDVDHWYGsY5IWfgFMiwv6A_Kyu3om9l3ovYSoj1ta0YRw&amp;oe=6A5D72BA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
+          <t>5½ (3 chambres fermées), 1100 pi² - Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
+          <t>3984, rue De Bullion, Montréal (H2W 2E4)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -2197,29 +2197,29 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-au-plateau-three-3-bedroom-apartment-in-plateau/1740633307</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
+          <t>Chauffage électrique non inclus, animaux acceptés, planchers bois franc, électroménagers inclus, dispo 1er août 2026 (bail 1 an)</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/64/64cccc9c-2b44-43ab-bc78-5ef6a4df00f6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
+          <t>Grand 6½ (3 chambres), 2 balcons, à 3 min du métro Jarry - Villeray</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
+          <t>n/d (Montréal, QC H2R 2E8, 2e étage)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Mary Two-Axe Earley (à vérifier)</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -2284,29 +2284,29 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-6-1-2-villeray-metro-jarry/1740626046</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
+          <t>Dispo 1er août 2026, non-fumeur, animaux non permis, lave-vaisselle/frigo inclus, laveuse-sécheuse dans l'unité, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/46/46364391-a0b3-4fdb-9a03-1b6d1cac4468?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2316,27 +2316,27 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
+          <t>Grand 5½ 3 chambres fermées, balcon avant/arrière - près métro Fabre (Villeray)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
+          <t>Villeray (adresse exacte n/d), Montréal</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>n/d (bus ~20 min)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -2371,29 +2371,29 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-3cac-metro-fabre-villeray-rosemont/1739951076</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
+          <t>6-plex, climatisation, sécurité 24h/concierge, stationnement vélo, station BIXI proche, chats acceptés seulement, non-fumeur, dispo 1er juillet 2026, chauffage non inclus</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2a/2a8f9aa3-ccb1-4d96-b244-4a697637e49c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2403,32 +2403,32 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
+          <t>Grand 6 1/2 rénové, terrasse privée – Villeray, près métro Crémazie</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>1695 Avenue Bourbonnière, Montréal</t>
+          <t>n/d (Montréal, QC H2P 2G9, secteur parc Jarry)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2438,49 +2438,49 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Joliette/Pie-IX</t>
+          <t>Crémazie</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/a-louer:-appartement-6-1-2-dans-villeray/1738327789</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
+          <t>Grande terrasse privée arrière + balcons avant/arrière, cuisine et salle de bain rénovées (douche romaine, puits de lumière), 4 électros + lave-vaisselle inclus, chauffage et eau chaude inclus (160$/mois fixe), piste cyclable devant, dispo 1er juillet 2026, bail 1 an</t>
         </is>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c339486c-6795-4d47-bcc5-625d60d299a0?rule=kpetroleumica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
+          <t>6 et demi avec cour arrière privative - Villeray - 1er juillet!</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
+          <t>8413 rue Saint-Hubert, Montréal, QC H2P 1Z6</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2520,22 +2520,22 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2545,29 +2545,29 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-et-demi-avec-cour-arriere-privative-villeray-1er-juillet/1734943312</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
+          <t>Dispo 1er juillet 2026, prix promo 12 mois (régulier 2050$), RDC + sous-sol aménagé, cour arrière privée, lave-vaisselle inclus, option 4 électros +100$/mois, 1 chat ou petit chien accepté</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8a/8a62cfb1-09e6-4e8b-bc96-fe68a77e35b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2577,80 +2577,84 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
+          <t>Beau 6 1/2 ensoleillé - proche metro - Hochelaga</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>3439 Rue William-Tremblay, Montréal</t>
+          <t>Montréal, QC H1W 1M3</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Joliette</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>verte</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/beau-6-1-2-ensoleille-proche-metro-hochelaga/1738000997</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="inlineStr"/>
+          <t>Dispo 1er juin 2026, eau incluse, 4 électros inclus (frigo cuisinière laveuse sécheuse), 2e étage, plafonds hauts, animaux limités, près Promenade Ontario</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/77/77a71464-4b91-4435-bf29-e86a1a84a6a8?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2660,32 +2664,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
+          <t>5 1/2 balcon, 3 chambres – Rosemont (14e Avenue / Masson)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2484 Rue Marie-Anne Est, Montréal</t>
+          <t>n/d (Montréal, QC H1X 2W2, secteur 14e Avenue/Masson)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2695,45 +2699,49 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-beds-2-baths-apartment/1740599440</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="inlineStr"/>
+          <t>Unité au rez-de-chaussée d'un duplex/triplex, salon-solarium lumineux, cour arrière privée, garage intérieur + stationnement extérieur, climatisation, pas d'animaux, dispo 1er août 2026</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/69/69d4ef7d-f6c5-401d-a2f8-9ca904eb6639?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2743,27 +2751,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
+          <t>6½ lumineux, 3 chambres fermées, rénové et équipé - Rosemont</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H1W 3A8</t>
+          <t>5838, avenue Louis-Hébert, Montréal</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2773,24 +2781,24 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Rosemont ou Beaubien (à vérifier)</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Joliette</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Kijiji</t>
@@ -2798,7 +2806,7 @@
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/6-lumineux-3-ch-fermees-renove-equipe-rosemont/1740407731</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2808,19 +2816,19 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
+          <t>Sous-location jusqu'au 31 juillet 2027, dispo 11 juillet 2026, 2 thermopompes (chauffage/clim), électroménagers neufs, animaux limités</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/55/5508505f-2676-403c-a0ef-0ff508313938?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -2830,27 +2838,27 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
+          <t>5½ rénové (2 chambres + bureau fermé), balcon arrière - rue Saint-Denis (Villeray)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>3602 rue de Rouen, Montréal</t>
+          <t>8360 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2865,27 +2873,27 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2 (estimé)</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-8360-st-denis-1132893</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -2895,15 +2903,19 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="inlineStr"/>
+          <t>Entièrement rénové 2024, électroménagers haut de gamme, walk-in, porte-patio, balcon arrière sur ruelle tranquille, dispo 1er sept. 2026, 2e étage</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132893/5-1-2-villeray-st-michel-parc-extension-600-15673596.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2913,27 +2925,27 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
+          <t>3 chambres, 1000 pi², 2 balcons - rue de Bellechasse (Rosemont)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>secteur métro Beaubien, H2S 2J5</t>
+          <t>4224 Rue de Bellechasse, Montréal</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2948,27 +2960,27 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Fabre (à vérifier)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/9945663</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
@@ -2978,12 +2990,12 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
+          <t>2 balcons (avant/arrière), aire ouverte lumineuse, 1 stationnement extérieur, Walk Score 85, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1173DFDDDDDDDDDDF&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -3000,32 +3012,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Rosemont rénové avec cour privée</t>
+          <t>Grand 5 1/2 lumineux, 1100 pi2 - à 200 m du métro Laurier</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -3035,7 +3047,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Rosemont</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -3045,7 +3057,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -3055,7 +3067,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
@@ -3065,19 +3077,19 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
+          <t>À 200 m (~2 min) du métro Laurier selon la fiche, disponible 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3087,32 +3099,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
+          <t>4 1/2 avec grand balcon, électros et clim inclus – Hochelaga</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>rue Marie-Anne, H2H 1M9</t>
+          <t>n/d (Montréal, QC H1W 3N5)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3122,17 +3134,17 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Joliette ou Pie-IX</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
@@ -3142,7 +3154,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-4-1-2-avec-balcon-electros-ac-inclus/1740573339</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
@@ -3152,19 +3164,19 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
+          <t>2 chambres fermées + boudoir, grand balcon arrière donnant sur jardin tranquille, électros neufs inclus (laveuse-sécheuse, lave-vaisselle, thermopompe), cuisine rénovée comptoir marbre, sdb rénovée 2025, internet haute vitesse inclus, sécurité 24h, non-fumeur, pas d'animaux, enquête de crédit, dispo 1er août 2026</t>
         </is>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/4c/4cb38191-e06a-433d-ad8f-fce80a96fe75?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3174,62 +3186,62 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
+          <t>Superbe 4 1/2, près métro Jarry – Villeray</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2017, avenue Letourneux, app. 101, Montréal</t>
+          <t>Avenue des Belges, Montréal, QC H2P 2B1</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/superbe-4-1-2-disponible-des-le-1er-septembre/1739673965</t>
         </is>
       </c>
       <c r="O32" s="5" t="inlineStr">
@@ -3239,12 +3251,12 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
+          <t>Cour arrière privée, tous électros inclus (cuisinière, frigo, lave-vaisselle, laveuse-sécheuse), climatisation, stationnement dans la rue, proche épiceries/pharmacie/restos/parcs, dispo 1er sept 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/a6/a6a41b4d-bb53-4c62-a720-a074f2806f46?rule=kijijica-640-webp</t>
         </is>
       </c>
     </row>
@@ -3261,27 +3273,27 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
+          <t>5 1/2 balcon, 1200 pi² – Rosemont</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>3477 rue Saint-Dominique, H2X 2X5</t>
+          <t>6885 43e Avenue, Montréal, QC H1T 2R9</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -3296,17 +3308,17 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Mary Two-Axe Earley (à vérifier)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -3316,7 +3328,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/3-bedroom-apartment-for-rent-in-rosemont/1739297378</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3326,19 +3338,19 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
+          <t>Animaux permis, eau chaude incluse, électricité et internet à la charge du locataire, libre 16 juin 2026, nom de station à vérifier</t>
         </is>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/2e/2efd08ab-2014-42f0-bde7-3afc97ccb893?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3348,27 +3360,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 3 chambres, 1085 pi² - avenue d'Orléans (Hochelaga), près métro Joliette</t>
+          <t>5 1/2 style condo, 2 balcons – Rosemont (Promenade Masson)</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2435 Avenue d'Orléans, Montréal, QC H1W 3S3</t>
+          <t>n/d (Montréal, QC H1Y 1Y3, secteur Promenade Masson)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -3378,22 +3390,22 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>n/d (bus ~20 min)</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3403,29 +3415,29 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-a-louer-un-beau-5-1-2-de-3-chambres-fermees-avec-garage/1736086864</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cessation-de-bail-5-style-condo-promenade-masson-rosemont/1739478440</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée d'un triplex, 1 stationnement privé inclus, accès cour arrière, non meublé, pas d'animaux, dispo 1er juillet 2026, à 450 m (~5 min) du métro Joliette et 600 m (~7 min) de Pie-IX</t>
+          <t>Chiens et chats acceptés, chauffage non inclus, Walk Score 99, très proche des commerces de la Promenade Masson</t>
         </is>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/03/03d8944a-7b26-4350-b716-ca7ec27241fb?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/21/219d597c-7a1f-471a-9c6c-a7768c42324c?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3435,22 +3447,22 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
+          <t>4 1/2 rénové, grand balcon, près métro Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>7186 Rue d'Iberville, Montréal</t>
+          <t>1695 Avenue Bourbonnière, Montréal</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -3470,17 +3482,17 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Joliette/Pie-IX</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>3 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
@@ -3490,29 +3502,29 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
+          <t>https://duproprio.com/fr/location/montreal/mercier-hochelaga-maisonneuve/4-1-2-a-louer/hab-1695-avenue-bourbonniere-1135855</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
+          <t>2 ch fermées (1 grande chambre double) + salle d'eau, grand balcon arrière sur jardin paisible, dispo 1er août 2026 (ou 18 juillet), à 1 min du Metro épicerie, 3 min boulangerie Arhoma, Promenade Ontario et Place Simon-Valois à pied</t>
         </is>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135855/mercier-hochelaga-maisonneuve-600-15749477.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3522,84 +3534,84 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
+          <t>Grand 5 1/2 rénové au RDC, près métro Pie-IX – Rosemont</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>3528 Avenue Coloniale, Montréal</t>
+          <t>4419 Avenue Charlemagne, Montréal, QC H1X 2H2</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-5-1-2-renove-a-louer-au-rdc-a-rosemont/1740506864</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
-        </is>
-      </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
+          <t>Climatisation incluse, fumage autorisé, pas d'animaux, aucun stationnement inclus, dispo 1er juillet 2026, proche Jardin botanique/Biodôme/Promenade Masson</t>
         </is>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/1d/1d7cfe92-1f54-4f36-9a36-2e82fab03b52?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3609,32 +3621,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
+          <t>Condo 5½ meublé, balcon vue sur parc – Angus/Rosemont, près métro Joliette</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud/Village)</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
+          <t>3439 Rue William-Tremblay, Montréal</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3644,7 +3656,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Papineau ou Beaudry</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -3654,39 +3666,35 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>9 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
+          <t>https://www.logisquebec.com/condo-a-louer-rosemont_la-petite-patrie-l353563</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
-        </is>
-      </c>
+          <t>Unité de coin entièrement meublée (TV, lit, sofa, climatiseur portatif, électros inclus), vue sur parc, arrêt de bus à 1 min vers le métro, électricité et internet en sus (~70$/mois chacun), dispo 1er août ou 1er sept 2026, secteur Angus vivant (écoles, parcs, commerces à pied)</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3696,32 +3704,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
+          <t>Condo 4½ neuf sur 2 étages, semi-meublé, balcon – Plateau/Centre-Sud, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>3845 rue Hochelaga (H1W 1J5)</t>
+          <t>2484 Rue Marie-Anne Est, Montréal</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -3731,7 +3739,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -3741,39 +3749,35 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
+          <t>https://www.logisquebec.com/condo-a-louer-le-plateau-mont-royal-l353552</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
-        </is>
-      </c>
+          <t>Condo construit en 2019, climatisation centrale, système d'alarme, entrées laveuse-sécheuse, dispo 1er sept 2026, station Frontenac aussi accessible à 12 min</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3783,84 +3787,84 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
+          <t>Appartement 3 chambres, jardin, parking, Hochelaga</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>5048 rue Rivard (H2J 2M9)</t>
+          <t>Montréal, QC H1W 3A8</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-3-chambres-jardin-parking-hochelaga/1739953364</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
+          <t>Cession de bail jusqu'au 1er juillet 2027, dispo 1er sept 2026, cour privée, stationnement, rangement au sous-sol, lave-vaisselle inclus, animaux limités, enquête de crédit</t>
         </is>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/43/4348c9c2-4f70-41ce-a65d-9ed5490935cd?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3870,79 +3874,75 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
+          <t>5½ meublé tout inclus à 3 min du métro Joliette</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
+          <t>3602 rue de Rouen, Montréal</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-mercier_hochelaga-maisonneuve-l353091</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
-        </is>
-      </c>
+          <t>5½ 900 pi² meublé, chauffé, wifi et tout inclus, grande terrasse arrière 100 pi², métro Joliette à 287 m, disponible 11 octobre 2026, bail min 3 mois, pas d'animaux</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3957,32 +3957,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
+          <t>5 1/2 + annexe rénové près du métro Beaubien</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2G 2S1)</t>
+          <t>secteur métro Beaubien, H2S 2J5</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -4012,29 +4012,29 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-annexe-renove-pres-du-metro-beaubien/1735720589</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
+          <t>3 ch fermées + annexe (ancien solarium), rénové récemment, 2 grands balcons, entrées laveuse-sécheuse et lave-vaisselle, climatisation, dispo 1er sept 2026, rue Beaubien et commerces à pied, non-fumeur, pas d'animaux</t>
         </is>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/ca/ca9a1937-a625-413b-ba4b-233b3a0e900b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Appartement lumineux sur la plaza</t>
+          <t>5 1/2 Rosemont rénové avec cour privée</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>rue Saint-Hubert, H2S 2L9</t>
+          <t>9e Avenue, Montréal, QC H1Y 2J9</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
@@ -4099,22 +4099,22 @@
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-rosemont-renove-avec-cour-privee/1739626532</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
+          <t>Cour privée avec cabanon, climatisation incluse, animaux acceptés, non meublé, dispo 1er août 2026, bail 1 an, Vieux Rosemont, walk score 10/10</t>
         </is>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/0d/0d2593ae-6698-452f-a94e-40f11723e9a8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ rénové avec stationnement</t>
+          <t>Magnifique 5 1/2 sur le plateau mont-royal</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Rosemont/La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>6855, rue d'Iberville, Montréal</t>
+          <t>rue Marie-Anne, H2H 1M9</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -4166,42 +4166,42 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>D'Iberville</t>
+          <t>Mont-Royal</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/magnifique-5-1-2-sur-le-plateau-mont-royal/1734803750</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>DuProprio</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
+          <t>3 ch fermées, cuisine rénovée comptoirs quartz, planchers bois franc d'origine, laveuse-sécheuse dans l'unité, balcon privé, animaux acceptés, bail au mois, avenue Mont-Royal et ses commerces à pied, chauffage/électricité en sus</t>
         </is>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/38/389e0d3d-7bcf-42a9-8fe4-8a27fa531359?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
+          <t>Unité neuve 3 chambres 1120 pi2 projet boutique</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4228,17 +4228,17 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>1841 Rue Saint-Germain, Montréal</t>
+          <t>2017, avenue Letourneux, app. 101, Montréal</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4273,22 +4273,22 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/27359064</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
+          <t>Construction neuve 2026, 6 pièces, 3 chambres en demi-sous-sol, terrasse commune sur le toit, semi-meublé, internet inclus, 1 mois gratuit bail 24 mois, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA15A15CDDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -4305,27 +4305,27 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
+          <t>Plateau - Superbe 5 1/2 de 3 Chambres - Disponible le 1er Juillet</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
+          <t>3477 rue Saint-Dominique, H2X 2X5</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -4340,17 +4340,17 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/plateau-superbe-5-1-2-de-3-chambres-disponible-le-1er-juillet/1740256791</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+          <t>3 ch fermées, 2e étage, laveuse-sécheuse dans l'unité, climatisation, balcon arrière, boul. Saint-Laurent et ses commerces à 1 rue, secteur sud du Plateau (limite Milton-Parc), métro Sherbrooke ou Saint-Laurent à pied, dispo 1er juillet 2026, animaux limités, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/8d/8d95567f-3a46-42b2-bcd6-c8ea29c0a1ff?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -4392,62 +4392,62 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
+          <t>5½ rénové 3 chambres, 1085 pi² - avenue d'Orléans (Hochelaga), près métro Joliette</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>8478 Rue Saint-Dominique, Montréal</t>
+          <t>2435 Avenue d'Orléans, Montréal, QC H1W 3S3</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Jarry ou Crémazie</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-a-louer-un-beau-5-1-2-de-3-chambres-fermees-avec-garage/1736086864</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -4457,19 +4457,19 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
+          <t>Rez-de-chaussée d'un triplex, 1 stationnement privé inclus, accès cour arrière, non meublé, pas d'animaux, dispo 1er juillet 2026, à 450 m (~5 min) du métro Joliette et 600 m (~7 min) de Pie-IX</t>
         </is>
       </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/03/03d8944a-7b26-4350-b716-ca7ec27241fb?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 Villeray . Christophe-Colomb.</t>
+          <t>5½ rénové 2024, balcon arrière avec toit - rue d'Iberville (Villeray), à deux pas du métro</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
+          <t>7186 Rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -4514,27 +4514,27 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3 (estimé)</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7186-rue-diberville-1078665</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -4544,19 +4544,19 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
+          <t>Rénové au complet printemps 2024, cuisine neuve comptoirs quartz, salle de bain avec plancher chauffant, 2e étage duplex, animaux non permis, dispo immédiatement, climatisation</t>
         </is>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202407/1078665/5-1-2-villeray-st-michel-parc-extension-1024-14442070.jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -4566,22 +4566,22 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 1000 pi², cour privée exclusive - boulevard Rosemont</t>
+          <t>4½ semi-meublé, 2 balcons, entre métro Sherbrooke et Saint-Laurent</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>n/d (Boul. Rosemont, Montréal, QC H1Y 1M5)</t>
+          <t>3528 Avenue Coloniale, Montréal</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Rosemont (à vérifier, adresse exacte non précisée)</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -4611,32 +4611,32 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-rosemont-la-petite-patrie/1740125612</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/18661844</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>Entièrement rénové, climatisation incluse, cour privée exclusive aux locataires, animaux (chiens) acceptés, aucun stationnement inclus, bail 1 an, dispo 1er août 2026, distance au métro incertaine (adresse précise non indiquée dans l'annonce)</t>
+          <t>Métro Sherbrooke à 600 m et Saint-Laurent à 650 m, balcons avant et arrière, laveuse-sécheuse inclus, pas d'animaux, dispo 1er mai 2026, prix à la limite haute du budget</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f6/f6ba5694-b433-4ed1-9bc1-e245d25714b2?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DADE9AF4DDDDDDDDDDF&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -4653,27 +4653,27 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
+          <t>3 chambres sur 2 niveaux, balcon - Ville-Marie (Village)</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Ville-Marie (Centre-Sud/Village)</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>7639 Rue Saint-Hubert, Montréal</t>
+          <t>1556 Rue Alexandre-de-Sève, Montréal, QC H2L 2V7</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -4683,47 +4683,47 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon ou Jarry (à vérifier)</t>
+          <t>Papineau ou Beaudry</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>5 (estimé)</t>
+          <t>9 (estimé)</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
+          <t>https://www.facebook.com/marketplace/item/1630277048041333</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
+          <t>3 chambres dont 1 à l'étage, chauffage électrique, entrée laveuse-sécheuse, chats acceptés, dispo 1er juillet 2026, secteur Village/Centre-Sud vivant. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/725664382_1806177020753109_738596762216669759_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=hMJqNHPfDaQQ7kNvwHanUl6&amp;_nc_oc=AdpnG9QIBpMUJP1wxwaIP0X85-sgqMS8IFmOP-dnQWyAx6A2jhbJOLq1E29TYkdqoAE&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQD44GmDh0ZUBIbweWf4W2TRvVKQ2s7WqU07gK4fjl_jSQ&amp;oe=6A5EA584</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
+          <t>Grand 5 1/2 sur 2 étages, 3 chambres et cour</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
+          <t>3845 rue Hochelaga (H1W 1J5)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -4785,32 +4785,32 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
+          <t>https://www.facebook.com/marketplace/item/1008792698770049</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
+          <t>5 1/2 sur 2 étages, 3 chambres, 2 balcons, cour, frigo/four/laveuse/sécheuse inclus, Centris 20702727, dispo maintenant. À l'ouest de Pie-IX, ~9 min à pied du métro Joliette (estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/714003647_2185734145539346_3198406513208048496_n.jpg?stp=dst-jpg_tt6&amp;cstp=mx1185x1184&amp;ctp=p526x296&amp;_nc_cat=110&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rWfRdyAQT2kQ7kNvwEDuxFQ&amp;_nc_oc=Adq1kZ7UKEWJ5AOUtBADQ2wc5Tm0xR6Oy1Es11qxDrIBpg5pQoUKzI5WditEAwUixfk&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCJsY2PUIFfIFE0IQOeFTV9m-V9fFS4ilU1C3PB62_vlg&amp;oe=6A5D9B7D</t>
         </is>
       </c>
     </row>
@@ -4827,32 +4827,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
+          <t>4 1/2 meublé 900 pi2 à 1 min du métro Laurier</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
+          <t>5048 rue Rivard (H2J 2M9)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -4882,22 +4882,22 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
+          <t>https://www.facebook.com/marketplace/item/1587980276170810</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
+          <t>4 1/2 rénové ~900 pi2 au rez-de-chaussée d'un triplex, entièrement meublé, climatisé, balcon privé, plafonds hauts, murs de briques. Moins d'1 min du métro Laurier et 5 min du parc Laurier selon la fiche, dispo immédiatement. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/741940752_1429328275740907_6698802259517172647_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=107&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=NMJOpVG6Y_4Q7kNvwELOmkA&amp;_nc_oc=AdqF3ydxe4mehyA40f7h2lZcCrSH8BQaQ3F2n0E8sKJGfnxgRh1HnvSvZ0FZQi_Zkow&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fFR5ChQi4J0gvgJw_ex77g&amp;_nc_ss=7f2a8&amp;oh=00_AQCS-CkFmscQOqIBqcnBnG2S49uR4g2vcHCV2VfWwe5WxQ&amp;oe=6A5D7C9F</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
+          <t>Grand 5 1/2 de 1144 pi2 près métro Fabre – Villeray</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Rue Sewell (H2W 1V9)</t>
+          <t>Secteur Villeray/Chabot (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Fabre</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -4969,29 +4969,29 @@
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
+          <t>https://www.facebook.com/marketplace/item/1218591924670571</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
+          <t>5 1/2 de 1144 pi2 au rez-de-chaussée d'un quadruplex : 3 grandes chambres fermées, thermopompe (clim+chauffage), électros et plusieurs meubles inclus, entrées laveuse/sécheuse. Près de la Plaza St-Hubert, quelques minutes du métro Fabre selon la fiche (~10 min estimé). Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/734897156_4591064421106932_6131094476647339162_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=LiymDaMlxe8Q7kNvwF9a4Tf&amp;_nc_oc=AdrV-_Dz-gdjZ96oH23Qhwdwu5Qhj3MRppo88SmiXkIuWNqL-8z-Z9b95F2mAAFuqkE&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQBvEs9zXVGz2UAd0G1bVEdU9X0Ch7Zxs8p4B_vnanFYNQ&amp;oe=6A5D7E3A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -5001,27 +5001,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
+          <t>5 1/2 lumineux, 2 chambres fermées, 2 balcons – Rosemont, près Cinéma Beaubien</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
+          <t>n/d (Montréal, QC H2G 2S1)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>8 (estimé)</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-lumineux-2-ch-fermees-renove-rosemont-petite-patrie/1739560132</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
+          <t>Animaux limités, 3e étage, buanderie et lave-vaisselle inclus, à deux pas du Cinéma Beaubien, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c1/c15d7c88-4278-46b2-b504-86cd39d6404b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5088,27 +5088,27 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
+          <t>Appartement lumineux sur la plaza</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>La Petite-Patrie</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
+          <t>rue Saint-Hubert, H2S 2L9</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -5118,22 +5118,22 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Pie-IX</t>
+          <t>Beaubien</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
@@ -5143,22 +5143,22 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-lumineux-sur-la-plaza/1739853332</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
+          <t>2 ch fermées + boudoir avec grand placard, Plaza St-Hubert au pied de l'immeuble (quartier très vivant), laveuse-sécheuse dans l'unité, clim, 1 stationnement, grand balcon, métro Beaubien à 2 min selon l'annonce, dispo 15 juillet 2026, animaux limités</t>
         </is>
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/29/29f42067-d07c-42c9-9127-b218f6f690f8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5175,27 +5175,27 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
+          <t>Condo 4½ rénové avec stationnement</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont/La Petite-Patrie</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2J 2Y3)</t>
+          <t>6855, rue d'Iberville, Montréal</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -5205,54 +5205,54 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>oui (petit balcon cuisine)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>D'Iberville</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>bleue</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
+          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/4-1-2-a-louer/hab-6855-diberville-1136946</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
+          <t>2 chambres fermées, cuisine et sdb modernes, climatisé, stationnement, rangement ext., animaux acceptés, dispo 16 juillet 2026</t>
         </is>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202607/1136946/4-1-2-rosemont-petite-patrie-600-15776920.jpg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -5262,22 +5262,22 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
+          <t>6 1/2, balcon et terrasse, animaux acceptés – Hochelaga</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
+          <t>1841 Rue Saint-Germain, Montréal</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Joliette</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
+          <t>https://centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
+          <t>Semi-meublé, animaux acceptés sous conditions (chiens ok), 1 stationnement, libre 7 jours après acceptation du bail, vérification de crédit requise</t>
         </is>
       </c>
       <c r="Q56" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -5349,22 +5349,22 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>5½ 2e étage Jarry Est rénové</t>
+          <t>Cession de bail – Grand 5 1/2 lumineux, balcon et terrasse – Hochelaga/Préfontaine</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>582 rue Jarry Est, Montréal</t>
+          <t>n/d (Montréal, QC H1V 2X2, secteur Préfontaine)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5384,45 +5384,49 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>LogisQuébec</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/cession-de-bail-grand-5-1-2-lumineux-hochelaga-prefontaine/1739376269</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
-        </is>
-      </c>
-      <c r="Q57" s="5" t="inlineStr"/>
+          <t>1er mois gratuit, animaux acceptés (même chiens), hydro et stationnement inclus, buanderie, bail jusqu'en juin 2027</t>
+        </is>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/9b/9b7ac581-3ab1-482b-9f87-d703dcb6bcc3?rule=kijijica-960-jpg</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -5432,7 +5436,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
+          <t>Condo 4½ meublé avec stationnement, près métro Jarry/Crémazie – Villeray</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -5442,17 +5446,17 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>8325B Rue Foucher, Montréal</t>
+          <t>8478 Rue Saint-Dominique, Montréal</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>930</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -5467,7 +5471,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Jarry ou Crémazie</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -5477,39 +5481,39 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
+          <t>5 (estimé)</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>DuProprio</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-8478-saint-dominique-1134387</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>Centris</t>
-        </is>
-      </c>
-      <c r="N58" s="7" t="inlineStr">
-        <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
+          <t>Meublé (TV 65po, mobilier complet), stationnement intérieur inclus, thermopompe, animaux négociables, bail min 12 mois, dispo 1er juillet 2026, hydro ~75$/mois + assurance 25$/mois en sus</t>
         </is>
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1134387/4-1-2-villeray-st-michel-parc-extension-600-15713346.jpg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -5519,27 +5523,27 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
+          <t>4 1/2 Villeray . Christophe-Colomb.</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>6904 Rue Hutchison, Montréal</t>
+          <t>Jarry/Christophe-Colomb, Montréal, QC H2P 0C3</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -5554,7 +5558,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Parc ou Acadie</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -5564,39 +5568,39 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-1-2-villeray-christophe-colomb/1739980393</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
+          <t>Dispo 1er sept 2026, internet et clim inclus, tous électros inclus (four frigo lave-vaisselle laveuse-sécheuse), animaux acceptés, immeuble béton insonorisé avec gym/ascenseur/concierge, grand balcon-terrasse privé</t>
         </is>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/5d/5d7a6647-dba7-4661-87c0-6b86eeb875b6?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -5606,22 +5610,22 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
+          <t>5½ rénové 1000 pi², cour privée exclusive - boulevard Rosemont</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>5342 Rue Saint-Denis, Montréal</t>
+          <t>n/d (Boul. Rosemont, Montréal, QC H1Y 1M5)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -5641,7 +5645,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Laurier</t>
+          <t>Rosemont (à vérifier, adresse exacte non précisée)</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -5651,32 +5655,32 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>6 (estimé)</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/appartement-5-1-2-rosemont-la-petite-patrie/1740125612</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
+          <t>Entièrement rénové, climatisation incluse, cour privée exclusive aux locataires, animaux (chiens) acceptés, aucun stationnement inclus, bail 1 an, dispo 1er août 2026, distance au métro incertaine (adresse précise non indiquée dans l'annonce)</t>
         </is>
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/f6/f6ba5694-b433-4ed1-9bc1-e245d25714b2?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -5693,42 +5697,42 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
+          <t>5½ rénové 3 chambres, stationnement inclus - rue Saint-Hubert (Villeray), proche Jean-Talon/Jarry</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>3514 Avenue De Lorimier, Montréal</t>
+          <t>7639 Rue Saint-Hubert, Montréal</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal (à vérifier)</t>
+          <t>Jean-Talon ou Jarry (à vérifier)</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -5738,39 +5742,39 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>5 (estimé)</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>DuProprio</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/5-1-2-a-louer/hab-7639-rue-st-hubert-1132037</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
+          <t>Rez-de-chaussée, électroménagers inclus (cuisinière, climatiseur, lave-vaisselle, laveuse, réfrigérateur, sécheuse), 1 stationnement inclus, dispo immédiatement, balcon non précisé dans l'annonce</t>
         </is>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132037/5-1-2-villeray-st-michel-parc-extension-600-15655024.jpg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -5780,22 +5784,22 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
+          <t>Cession de bail 4 1/2 (2 ch. + bureau), 2 balcons, près métro Préfontaine</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>6904, 23e Avenue, Montréal</t>
+          <t>1841, Rue Saint-Germain, Montréal (Mercier/Hochelaga-Maisonneuve)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -5810,22 +5814,22 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>oui (terrasse sur le toit)</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Beaubien ou Rosemont (à vérifier)</t>
+          <t>Préfontaine</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
@@ -5835,22 +5839,22 @@
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-mercier-hochelaga-maisonneuve/25697495</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
+          <t>Cession de bail, 2e et dernier étage, semi-meublé avec électroménagers inclus, balcon avant + terrasse arrière, 1 stationnement (allée), animaux acceptés (chiens inclus), Walk Score 96, près rue Ontario (commerces/restos), disponible ~7 jours après acceptation</t>
         </is>
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA16F1EEDDDDDDDDDD4&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5871,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
+          <t>5 1/2 lumineux, 2 balcons – Villeray (rue de Castelnau Est)</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -5877,67 +5881,67 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>n/d (Montréal, QC H2R)</t>
+          <t>361 Rue de Castelnau Est, Montréal, QC H2R</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Talon</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>orange/bleue</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>Jarry</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.facebook.com/marketplace/item/4364819800401491</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
+          <t>3 chambres fermées, 2 salles de bain, 2 balcons, tous électros inclus + climatiseur, 1 animal accepté, à quelques pas de cafés/restos/commerces/parcs/épiceries, dispo 15 sept 2026, bail 1 an — lien Marketplace exige une connexion Facebook</t>
         </is>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/738175791_122163358448956236_8893879274479902982_n.jpg?stp=c181.0.1086.1086a_dst-jpg_tt6&amp;cstp=mx1086x1086&amp;ctp=s565x565&amp;_nc_cat=106&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=rpx2E0vyW3kQ7kNvwGfclmJ&amp;_nc_oc=AdpALm3YusJq0Maav6el9qX4etr-2lUMEAPvYv1MfGvC3tr715UbWgD4CmQchGPjt44&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=EBKM-YBwAXSEbwqv2KAm-A&amp;_nc_ss=7f2a8&amp;oh=00_AQALNx8M-H3ukcmH2qnLjQMRNiPmxzCkC373khtB7tqWEQ&amp;oe=6A5D6801</t>
         </is>
       </c>
     </row>
@@ -5954,52 +5958,52 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
+          <t>5 1/2 meublé 1200 pi2 avec cour – Plateau</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Secteur station Papineau (adresse exacte n/d)</t>
+          <t>Rue Sewell (H2W 1V9)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Papineau</t>
+          <t>Sherbrooke</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
@@ -6009,22 +6013,22 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
+          <t>https://www.facebook.com/marketplace/item/1019005031103806</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 avec électros inclus (frigo, poêle, laveuse, sécheuse), électricité et chauffage en sus. Métro Papineau à 5 min/350 m et Beaudry à 9 min/600 m selon la fiche. Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>5 1/2 meublé de 1200 pi2 : 2 chambres + pièce supplémentaire + salle de lavage, cour arrière privée, entrée privée, électros neufs, vue sur parc. 10 min à pied du métro Sherbrooke et de McGill selon la fiche, dispo 1er septembre. Lien Facebook (connexion requise)</t>
         </is>
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.84726-6/702570444_965981126154971_7860153536382112939_n.jpg?stp=c135.0.540.540a_dst-jpg_p180x540_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=92e707&amp;_nc_ohc=YneU80YO-OUQ7kNvwEMKKPR&amp;_nc_oc=AdqQpL92df6JuIzjTm69wGLTEPS_1V8hsWZAM0tXrGbWDNVejO5RWBTaXAMGV0_3PmA&amp;_nc_zt=14&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQBudC_waGB9vyBBikfqMR4ldQ2tCfCUG-jhdbBvYBGK7A&amp;oe=6A5DA048</t>
+          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/744858739_10165155610490786_1771055700003483249_n.jpg?stp=c342.0.1364.1364a_dst-jpg_tt6&amp;cstp=mx1364x1364&amp;ctp=s565x565&amp;_nc_cat=111&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=K4tM_CSheCoQ7kNvwEVm0M8&amp;_nc_oc=Adr-C6MeJfiuug8uyEwRuwdFFh7Xv6Ka03-bESw5VsBoVE8Y1b4CTD5PKQKPUfRJmO8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=yYLPvMa76LbSuFVLINSV0A&amp;_nc_ss=7f2a8&amp;oh=00_AQCNsVfbH6vfqg264B34f74Hj2CUebDBcYc18lipFA0U3A&amp;oe=6A5D6C01</t>
         </is>
       </c>
     </row>
@@ -6041,84 +6045,84 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Grand 6 1/2 rénové 4 chambres – rue Dézéry</t>
+          <t>4½ rénové, 1000 pi², près métro Laurier – Plateau (Parc-Lafontaine)</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Hochelaga-Maisonneuve</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>1478 rue Dézéry</t>
+          <t>4225 Rue de Lanaudière, Montréal, QC H2J 3N8</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Préfontaine</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>verte</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/tres-beau-4-recemment-renove-au-coeur-du-plateau-mont-royal/1739158104</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/996541189451973</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
-          <t>6 1/2 entièrement rénové, 4 chambres, laveuse et sécheuse incluses, près de la rue Ontario Est. La fiche mentionne le métro Viau mais l'adresse est en fait à ~6 min à pied de Préfontaine (ligne verte, à l'ouest de Pie-IX). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>2e étage, laveuse-sécheuse-poêle-frigo inclus, non-fumeur, pas d'animaux, aucun stationnement, dispo 1er juillet 2026, près parc La Fontaine, walk score 10/10</t>
         </is>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/720228177_1306788231541291_7590507790785404579_n.jpg?stp=c0.167.1543.1543a_dst-jpg_tt6&amp;cstp=mx1543x1543&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=946e27&amp;_nc_ohc=iZQOOaTW0cIQ7kNvwEyMuvN&amp;_nc_oc=Adp5JfNLtujsJ-FoPwyVSLHIsN4Fp1OHVYUjEZsKqZtTJ-zw9HiwKtu0-otG8pSV1Ug&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=DmO9x3asu-QmYjoryvRuXw&amp;_nc_ss=7f2a8&amp;oh=00_AQDrv_S-F8xizI4jJzIXeDM0ZqtsTCvZjjD9hMqbW4xx5g&amp;oe=6A5D930D</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/15/15437f31-23a1-4bd9-9a52-5d9b817ca005?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -6128,27 +6132,27 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové 2 chambres avec cour – Petite Italie</t>
+          <t>5 1/2 RDC rénové avec cour – Hochelaga, près Pie-IX</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>La Petite-Patrie</t>
+          <t>Hochelaga-Maisonneuve</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Rue Drolet entre St-Zotique et Bélanger</t>
+          <t>1711 Avenue d'Orléans, Montréal, QC H1W 3R4</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>900</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -6163,42 +6167,42 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Beaubien</t>
+          <t>Pie-IX</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
+          <t>10 (estimé)</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>Kijiji</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/hochelaga-superbe-5-1-2-renove-au-rez-de-chaussee-avec-cour/1740256793</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="N66" s="7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/marketplace/item/869673732860172</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
-          <t>4 1/2 rénové, 950 pi2, 2 chambres fermées avec rangements intégrés, cuisine rénovée avec îlot, grande cour arrière privée avec remise. Petite Italie, à deux pas du marché Jean-Talon. Lien Facebook (connexion requise)</t>
+          <t>Animaux limités, stationnement inclus, cour arrière privée, climatisation, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t45.5328-4/730120213_2240322190063726_502660368798558142_n.jpg?stp=c0.87.526.526a_dst-jpg_p526x395_tt6&amp;_nc_cat=103&amp;ccb=1-7&amp;_nc_sid=247b10&amp;_nc_ohc=hha1ljqLIIYQ7kNvwFKmpJ9&amp;_nc_oc=AdoS60VDWcE7lmKj0eEjd2YW_J4Fk9AcMc_aBx8zzKmkriEb4Tbdy0Qv9KMYCa3RHBM&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=jI9ZE0EjGyFqTM97Yzl5mA&amp;_nc_ss=7f2a8&amp;oh=00_AQC61rgjJ4mtmN97tFED2D60srRInJ_PPGwLKZaJWsd7xQ&amp;oe=6A5D81CB</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/d0/d0d75179-15a9-4d6e-a66c-024195759d32?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
@@ -6215,27 +6219,27 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 Villeray - 2 chambres - près du métro Jarry - 2050$</t>
+          <t>Grand 5 1/2 lumineux, à 200m du métro Laurier – Plateau</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Le Plateau-Mont-Royal</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Montréal, QC H2R</t>
+          <t>n/d (Montréal, QC H2J 2Y3)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -6245,12 +6249,12 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui (petit balcon cuisine)</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Jarry</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -6260,7 +6264,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
@@ -6270,29 +6274,29 @@
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/grand-51-2-lumineux-sur-plateau-mont-royal/1738318103</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
-          <t>Dispo 1er juin 2026, rénové, 2 chambres + bureau, thermopompe (chauffage/clim), 5 électros inclus, cour-patio arrière, planchers bois franc refaits, pas d'animaux</t>
+          <t>Chauffage inclus, animaux limités, walk-in dans chambre principale, libre 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/d0/d0ca9a85-dbf8-4673-a89d-264708952626?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -6302,7 +6306,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>5 1/2 rénové, 995 pi², près Promenade Masson – Rosemont</t>
+          <t>4 1/2 sur 2 étages, condo neuf « Joseph », balcon, près métro Joliette</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -6312,74 +6316,74 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>5472 1ere Avenue, Montréal</t>
+          <t>3420 boul. Saint-Joseph Est, Montréal, QC H1X 0A6</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>n/d</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>Joliette</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/rosemont-la-petite-patrie/5-1-2-a-louer/hab-5472-1ere-avenue-882773</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/4-5-sur-2-etages-condo-appartement-a-louer-rosemont-joseph/1727979165</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
-          <t>Chauffage au plancher radiant, climatisation, cour privée avec remise, près Promenade Masson et parc Pélican, non-fumeurs</t>
+          <t>Condo neuf « Joseph » sur 2 étages, face au parc Lafond, eau chaude et climatisation incluses, électros neufs (laveuse-sécheuse inclus), piscine extérieure/gym/stationnement intérieur payant, animaux acceptés, superficie non précisée, près Stade olympique et Jardin botanique</t>
         </is>
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/201911/882773/5-1-2-plateau-mont-royal-1600-10690669.jpg</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-dealer-ads/images/2a/2a378c4c-30df-42fd-8c0d-515e4ee71bc4?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -6389,22 +6393,22 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>4½ moderne, thermopompe - avenue Papineau (Centre-Sud)</t>
+          <t>5½ 2e étage Jarry Est rénové</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Ville-Marie (Centre-Sud)</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>2121 Avenue Papineau, app. 106, Montréal</t>
+          <t>582 rue Jarry Est, Montréal</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -6414,59 +6418,55 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>Papineau</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>verte</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr">
-        <is>
-          <t>11 (estimé)</t>
-        </is>
-      </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>LogisQuébec</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1345509854217640</t>
+          <t>https://www.logisquebec.com/appartement-a-louer-villeray_saint-michel_parc-extension-l353442</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
-          <t>Thermopompe (chauffage/climatisation), 5 électros inclus, stationnement intérieur +200$/mois, dispo 1er sept 2026. Lien Facebook (connexion requise)</t>
-        </is>
-      </c>
-      <c r="Q69" s="5" t="inlineStr">
-        <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/740967146_10163353758868282_6445879430357129287_n.jpg?stp=c267.0.1067.1067a_dst-jpg_tt6&amp;cstp=mx1067x1067&amp;ctp=s565x565&amp;_nc_cat=105&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=NBpCPM0lMZ0Q7kNvwEgcjRv&amp;_nc_oc=AdpKpJOW9gIXzADTI6MMd8QgF1AIUSvmXyA1OhFaypIfCHhp5Q_WLet_FlJK9JeWopU&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=po_Fub79cNJDfbGc2ZS1tQ&amp;_nc_ss=7f2a8&amp;oh=00_AQAYyDy-ZzVKaSsRH6KHfK-C3t6CRRIgCb8d-ae59ygZwA&amp;oe=6A5E8565</t>
-        </is>
-      </c>
+          <t>5½ 3 chambres fermées, rénové, climatisation murale, balcons avant et arrière, métro Jarry à 103 m, disponible immédiatement, enquête de crédit exigée</t>
+        </is>
+      </c>
+      <c r="Q69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>6 pièces, 3 chambres - rue Fabre (Rosemont)</t>
+          <t>Condo 4½ semi-meublé face au parc Père-Marquette - Rosemont</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -6486,32 +6486,32 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>6525 Rue Fabre, app. 2, Montréal</t>
+          <t>n/d (face au parc Père-Marquette, Montréal)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>970</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non (terrasse commune sur le toit)</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Beaubien (à vérifier)</t>
+          <t>Rosemont</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -6521,39 +6521,39 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/28139377</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/condo-4-a-louer-dans-rosemont-la-petite-patrie/1739545131</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, 1 stationnement (allée), Walk Score 95, dispo 7 jours après acceptation, station de métro non précisée par l'annonce</t>
+          <t>Semi-meublé, buanderie privée, lave-vaisselle, climatisation, rangement au sous-sol, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA149845DDDDDDDDDDD&amp;t=pi&amp;w=640&amp;h=480&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/c3/c32bb989-3256-4fd9-b5c7-30a77bfd8b2b?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6563,22 +6563,22 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Grand 4 chambres + bureau – St-André bas Plateau</t>
+          <t>4½ rénové 2024, balcon privé, dernier étage - rue Foucher (Villeray), près métro Jarry</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>3855 rue St-André (H2L 3V9)</t>
+          <t>8325B Rue Foucher, Montréal</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -6613,34 +6613,34 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/marketplace/item/1550150270173512</t>
+          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/20638950</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
-          <t>4 chambres (dont 1 sans fenêtre) + bureau fermé, électros inclus, dispo 1er juillet. ~7 min à pied du métro Sherbrooke (estimé depuis l'adresse). Superficie non indiquée. Lien Facebook (connexion requise)</t>
+          <t>Dernier étage sans voisin au-dessus, puits de lumière, chats acceptés, proche pharmacie/dépanneur/restos, dispo 1er juillet 2026</t>
         </is>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>https://scontent-yyz1-1.xx.fbcdn.net/v/t39.30808-6/728474326_10231683771185831_6727292866936668830_n.jpg?stp=c256.0.1537.1537a_dst-jpg_tt6&amp;cstp=mx1537x1537&amp;ctp=s565x565&amp;_nc_cat=100&amp;ccb=1-7&amp;_nc_sid=454cf4&amp;_nc_ohc=943KDXUX1RQQ7kNvwFf3aXH&amp;_nc_oc=AdqiIy58nJFG1aGG5u9HQW6_QOL-2IMomb6kZpX5RbtE63MiJU-sRJMxj6FOz1Mq-C8&amp;_nc_zt=23&amp;_nc_ht=scontent-yyz1-1.xx&amp;_nc_gid=fqv6VHej6TNF8DZvOf_nSw&amp;_nc_ss=7f2a8&amp;oh=00_AQDIA5orKA1mjUQENX8o5T3X6Cteocg2jKTYaTNLxvUcJw&amp;oe=6A5D72DF</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA1701B6DDDDDDDDDD0&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres, près métro Mont-Royal (rue de Bordeaux)</t>
+          <t>4½ rénové, balcon, à 5 min des métros Parc/Acadie</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray-Saint-Michel-Parc-Extension (secteur Parc-Extension)</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>4275 Rue de Bordeaux, Montréal</t>
+          <t>6904 Rue Hutchison, Montréal</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -6675,17 +6675,17 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal</t>
+          <t>Parc ou Acadie</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>10 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-4275-bordeaux-1131937</t>
+          <t>https://duproprio.com/fr/location/montreal/villeray-st-michel-parc-extension/4-1-2-a-louer/hab-6904-hutchison-1135219</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>2e étage, dispo immédiatement, rien d'inclus (chauffage/électricité aux frais du locataire), à moins de 10 min du parc La Fontaine, proche avenue du Mont-Royal (commerces/cafés), balcon et superficie non précisés dans l'annonce</t>
+          <t>2e étage, entrée privée, électros + climatiseur inclus, dispo immédiatement, proche campus MIL de l'UdeM et Marché Central. Secteur Parc-Extension plutôt que le coeur de Villeray.</t>
         </is>
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1131937/plateau-mont-royal-600-15652873.jpg</t>
+          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135219/4-1-2-villeray-st-michel-parc-extension-600-15733731.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>5 1/2, 3 chambres – Plateau (avenue de Lorimier)</t>
+          <t>Condo 4½ meublé 1000 pi², près métro Laurier</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -6747,32 +6747,32 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>4216 avenue de Lorimier, app. 204, Montréal</t>
+          <t>5342 Rue Saint-Denis, Montréal</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Mont-Royal ou Papineau (à vérifier)</t>
+          <t>Laurier</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
@@ -6782,39 +6782,39 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>12 (estimé)</t>
+          <t>6 (estimé)</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-204-4216-av-de-lorimier-1135328</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/21225046</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
-          <t>Semi-meublé, laveuse-sécheuse/cuisinière/frigo inclus, wifi inclus, 2e étage, petits animaux acceptés, dispo 1er juillet ou 1er sept 2026, balcon non précisé dans l'annonce, secteur commerçant (cafés, parcs) à pied</t>
+          <t>Meublé et équipé, 2e étage, Walk Score 99, proche piste cyclable REV, dispo 1er sept 2026</t>
         </is>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202606/1135328/5-1-2-plateau-mont-royal-600-15736059.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD700DBDDDDDDDDDDD&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Grand 5 1/2, 3 chambres fermées – coeur du Plateau (rue Rachel Est)</t>
+          <t>4½ semi-meublé, 2 balcons, secteur Marie-Anne/de Lorimier</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>62 rue Rachel Est, Montréal</t>
+          <t>3514 Avenue De Lorimier, Montréal</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -6849,17 +6849,17 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke ou Mont-Royal (à vérifier)</t>
+          <t>Mont-Royal (à vérifier)</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -6869,39 +6869,39 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>12 (estimé)</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>DuProprio</t>
+          <t>Centris</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>https://duproprio.com/fr/location/montreal/le-plateau-mont-royal/5-1-2-a-louer/hab-5-12-62-rue-rachel-est-1132358</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/25841083</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>Dernier étage, tranquille et lumineux, entrée laveuse-sécheuse, non-fumeur, chiens non acceptés, enquête de crédit requise, balcon et superficie non précisés dans l'annonce, secteur près Saint-Laurent/Saint-Denis</t>
+          <t>2 balcons, plafonds 9 pieds, double salon, animaux acceptés sous conditions, dispo 8 juin 2026, distance au métro estimée (non confirmée par l'annonce)</t>
         </is>
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>https://photos.duproprio.com/photos/public/for_rent/202605/1132358/5-1-2-plateau-mont-royal-1600-15661700.jpg</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DA140A2CDDDDDDDDDD4&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -6911,22 +6911,22 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Condo 2 chambres semi-meublé, stationnement intérieur - rue Villeray, à 9 min du métro Fabre</t>
+          <t>4½/5½ rénové avec terrasse sur le toit - 23e Avenue (Rosemont)</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Villeray</t>
+          <t>Rosemont-La Petite-Patrie</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>1414 Rue Villeray, app. 105, Montréal</t>
+          <t>6904, 23e Avenue, Montréal</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -6941,22 +6941,22 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>oui (terrasse sur le toit)</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Fabre</t>
+          <t>Beaubien ou Rosemont (à vérifier)</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>bleue</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10 (estimé)</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
@@ -6966,29 +6966,29 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/en/condos-apartments~for-rent~montreal-villeray-saint-michel-parc-extension/25583093</t>
+          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/21529896</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>Immeuble de 2011 (30 unités), RDC, plancher chauffant salle de bain, stationnement intérieur avec borne de recharge, casier de rangement, buanderie commune, terrasse sur le toit, Walk Score 94, dispo 1er juillet 2026</t>
+          <t>Immeuble annonçant des unités jusqu'à 1200 pi² (superficie exacte de cette unité non confirmée), terrasse sur le toit commune, stationnement intérieur +100$/mois, animaux sous conditions, 2 mois gratuits, dispo 1er avril 2026</t>
         </is>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DAD77D67DDDDDDDDDDB&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
+          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE5F3D7ADDDDDDDDDD2&amp;t=pi&amp;w=1260&amp;h=1024&amp;sm=c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -6998,27 +6998,27 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>4½ rénové, 2 chambres, à 3-4 min du métro Sherbrooke</t>
+          <t>5 1/2 rénové, 2 chambres, 1000 pi2 - près métro Jarry</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Le Plateau-Mont-Royal</t>
+          <t>Villeray</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>3711 Rue Saint-Urbain, app. A, Montréal</t>
+          <t>n/d (Montréal, QC H2R)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>n/d</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Sherbrooke</t>
+          <t>Jarry</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -7043,39 +7043,39 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-le-plateau-mont-royal/9588101</t>
+          <t>https://www.kijiji.ca/v-apartments-condos/ville-de-montreal/5-1-2-villeray-2-chambres-pres-du-metro-jarry-2050/1738384606</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>Cuisine et salle de bain rénovées, plafonds hauts, tous électros inclus, Walk Score 100, dispo 5 jours après acceptation, à 5 min de McGill</t>
+          <t>Porte-patio menant à une cour arrière (pas de balcon à proprement parler), disponible 1er juin 2026</t>
         </is>
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>https://mspublic.centris.ca/media.ashx?id=ADDD250DE6F28A2DDDDDDDDDDB&amp;t=pi&amp;w=1024&amp;h=640&amp;sm=c</t>
+          <t>https://media.kijiji.ca/api/v1/ca-prod-fsbo-ads/images/cf/cf44ffec-5a1f-4ffd-81e0-2eb0cfc316d8?rule=kijijica-960-jpg</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -7085,22 +7085,22 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Appartement meublé haut de gamme - avenue Henri-Julien (Rosemont), près marché Jean-Talon</t>
+          <t>5 1/2 à 5 min du métro Papineau – Ville-Marie/Le Village</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Rosemont-La Petite-Patrie</t>
+          <t>Ville-Marie (Centre-Sud)</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>6391 Avenue Henri-Julien, Montréal</t>
+          <t>Secteur station Papineau (adresse exacte n/d)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -7120,42 +7120,42 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Jean-Talon (à vérifier)</t>
+          <t>Papineau</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>orange/bleue</t>
+          <t>verte</t>
         </is>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>8 (estimé)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>Centris</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>https://www.centris.ca/fr/condo-appartement~a-louer~montreal-rosemont-la-petite-patrie/10049540</t>
+          <t>https://www.facebook.com/marketplace/item/1880955355936721</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+   